--- a/research/traditional_assets/database/data/finland/finland_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_healthcare_products.xlsx
@@ -1778,7 +1778,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1915,22 +1915,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09638866533241686</v>
+        <v>0.09623188800175202</v>
       </c>
       <c r="C2">
-        <v>745.7728688593302</v>
+        <v>740.5591941161966</v>
       </c>
       <c r="D2">
-        <v>730.6728688593302</v>
+        <v>732.9443075563111</v>
       </c>
       <c r="E2">
-        <v>-16.61134401144722</v>
+        <v>-9.12623057133275</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.485113440114473</v>
       </c>
       <c r="G2">
         <v>15.1</v>
@@ -1951,28 +1951,28 @@
         <v>27.071</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.376501206037758</v>
       </c>
       <c r="N2">
-        <v>27.071</v>
+        <v>26.69449879396224</v>
       </c>
       <c r="O2">
-        <v>5.4142</v>
+        <v>5.338899758792448</v>
       </c>
       <c r="P2">
-        <v>21.6568</v>
+        <v>21.35559903516979</v>
       </c>
       <c r="Q2">
-        <v>27.3968</v>
+        <v>27.09559903516979</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09638866533241686</v>
+        <v>0.09679746262803235</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.048561507391778</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>71.90149610645641</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1997,22 +1997,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09623188800175202</v>
+        <v>0.09607511067108719</v>
       </c>
       <c r="C3">
-        <v>740.5591941161966</v>
+        <v>735.3596858300206</v>
       </c>
       <c r="D3">
-        <v>732.9443075563111</v>
+        <v>735.2299127102494</v>
       </c>
       <c r="E3">
-        <v>-9.12623057133275</v>
+        <v>-1.641117131218277</v>
       </c>
       <c r="F3">
-        <v>7.485113440114473</v>
+        <v>14.97022688022895</v>
       </c>
       <c r="G3">
         <v>15.1</v>
@@ -2033,28 +2033,28 @@
         <v>27.071</v>
       </c>
       <c r="M3">
-        <v>0.376501206037758</v>
+        <v>0.753002412075516</v>
       </c>
       <c r="N3">
-        <v>26.69449879396224</v>
+        <v>26.31799758792448</v>
       </c>
       <c r="O3">
-        <v>5.338899758792448</v>
+        <v>5.263599517584897</v>
       </c>
       <c r="P3">
-        <v>21.35559903516979</v>
+        <v>21.05439807033958</v>
       </c>
       <c r="Q3">
-        <v>27.09559903516979</v>
+        <v>26.79439807033958</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09679746262803235</v>
+        <v>0.09721460272559918</v>
       </c>
       <c r="T3">
-        <v>1.048561507391778</v>
+        <v>1.057138346845311</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>71.90149610645641</v>
+        <v>35.9507480532282</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2079,22 +2079,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09607511067108719</v>
+        <v>0.09591833334042235</v>
       </c>
       <c r="C4">
-        <v>735.3596858300206</v>
+        <v>730.1744769449261</v>
       </c>
       <c r="D4">
-        <v>735.2299127102494</v>
+        <v>737.5298172652696</v>
       </c>
       <c r="E4">
-        <v>-1.641117131218277</v>
+        <v>5.843996308896195</v>
       </c>
       <c r="F4">
-        <v>14.97022688022895</v>
+        <v>22.45534032034342</v>
       </c>
       <c r="G4">
         <v>15.1</v>
@@ -2115,28 +2115,28 @@
         <v>27.071</v>
       </c>
       <c r="M4">
-        <v>0.753002412075516</v>
+        <v>1.129503618113274</v>
       </c>
       <c r="N4">
-        <v>26.31799758792448</v>
+        <v>25.94149638188673</v>
       </c>
       <c r="O4">
-        <v>5.263599517584897</v>
+        <v>5.188299276377346</v>
       </c>
       <c r="P4">
-        <v>21.05439807033958</v>
+        <v>20.75319710550938</v>
       </c>
       <c r="Q4">
-        <v>26.79439807033958</v>
+        <v>26.49319710550938</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09721460272559918</v>
+        <v>0.09764034364991994</v>
       </c>
       <c r="T4">
-        <v>1.057138346845311</v>
+        <v>1.065892028349433</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>35.9507480532282</v>
+        <v>23.96716536881881</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2161,22 +2161,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09591833334042235</v>
+        <v>0.09576155600975754</v>
       </c>
       <c r="C5">
-        <v>730.1744769449261</v>
+        <v>725.00370207373</v>
       </c>
       <c r="D5">
-        <v>737.5298172652696</v>
+        <v>739.8441558341879</v>
       </c>
       <c r="E5">
-        <v>5.843996308896195</v>
+        <v>13.32910974901067</v>
       </c>
       <c r="F5">
-        <v>22.45534032034342</v>
+        <v>29.94045376045789</v>
       </c>
       <c r="G5">
         <v>15.1</v>
@@ -2197,28 +2197,28 @@
         <v>27.071</v>
       </c>
       <c r="M5">
-        <v>1.129503618113274</v>
+        <v>1.506004824151032</v>
       </c>
       <c r="N5">
-        <v>25.94149638188673</v>
+        <v>25.56499517584897</v>
       </c>
       <c r="O5">
-        <v>5.188299276377346</v>
+        <v>5.112999035169794</v>
       </c>
       <c r="P5">
-        <v>20.75319710550938</v>
+        <v>20.45199614067917</v>
       </c>
       <c r="Q5">
-        <v>26.49319710550938</v>
+        <v>26.19199614067917</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09764034364991994</v>
+        <v>0.09807495417683076</v>
       </c>
       <c r="T5">
-        <v>1.065892028349433</v>
+        <v>1.074828078218225</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.96716536881881</v>
+        <v>17.9753740266141</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2243,22 +2243,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09576155600975754</v>
+        <v>0.09560477867909267</v>
       </c>
       <c r="C6">
-        <v>725.00370207373</v>
+        <v>719.8474975242071</v>
       </c>
       <c r="D6">
-        <v>739.8441558341879</v>
+        <v>742.1730647247795</v>
       </c>
       <c r="E6">
-        <v>13.32910974901067</v>
+        <v>20.81422318912514</v>
       </c>
       <c r="F6">
-        <v>29.94045376045789</v>
+        <v>37.42556720057237</v>
       </c>
       <c r="G6">
         <v>15.1</v>
@@ -2279,28 +2279,28 @@
         <v>27.071</v>
       </c>
       <c r="M6">
-        <v>1.506004824151032</v>
+        <v>1.88250603018879</v>
       </c>
       <c r="N6">
-        <v>25.56499517584897</v>
+        <v>25.18849396981121</v>
       </c>
       <c r="O6">
-        <v>5.112999035169794</v>
+        <v>5.037698793962242</v>
       </c>
       <c r="P6">
-        <v>20.45199614067917</v>
+        <v>20.15079517584897</v>
       </c>
       <c r="Q6">
-        <v>26.19199614067917</v>
+        <v>25.89079517584896</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09807495417683076</v>
+        <v>0.09851871439904493</v>
       </c>
       <c r="T6">
-        <v>1.074828078218225</v>
+        <v>1.083952255452675</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.9753740266141</v>
+        <v>14.38029922129128</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2325,22 +2325,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09560477867909267</v>
+        <v>0.09552000134842785</v>
       </c>
       <c r="C7">
-        <v>719.8474975242071</v>
+        <v>713.6278597400117</v>
       </c>
       <c r="D7">
-        <v>742.1730647247795</v>
+        <v>743.4385403806984</v>
       </c>
       <c r="E7">
-        <v>20.81422318912514</v>
+        <v>28.29933662923962</v>
       </c>
       <c r="F7">
-        <v>37.42556720057237</v>
+        <v>44.91068064068684</v>
       </c>
       <c r="G7">
         <v>15.1</v>
@@ -2361,45 +2361,45 @@
         <v>27.071</v>
       </c>
       <c r="M7">
-        <v>1.88250603018879</v>
+        <v>2.326373257187578</v>
       </c>
       <c r="N7">
-        <v>25.18849396981121</v>
+        <v>24.74462674281242</v>
       </c>
       <c r="O7">
-        <v>5.037698793962242</v>
+        <v>4.948925348562485</v>
       </c>
       <c r="P7">
-        <v>20.15079517584897</v>
+        <v>19.79570139424994</v>
       </c>
       <c r="Q7">
-        <v>25.89079517584896</v>
+        <v>25.53570139424994</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09851871439904493</v>
+        <v>0.09897191632811474</v>
       </c>
       <c r="T7">
-        <v>1.083952255452675</v>
+        <v>1.093270564117645</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.38029922129128</v>
+        <v>11.63656774181067</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2407,22 +2407,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09552000134842785</v>
+        <v>0.09537522401776302</v>
       </c>
       <c r="C8">
-        <v>713.6278597400117</v>
+        <v>708.3138519181211</v>
       </c>
       <c r="D8">
-        <v>743.4385403806984</v>
+        <v>745.6096459989225</v>
       </c>
       <c r="E8">
-        <v>28.29933662923961</v>
+        <v>35.78445006935408</v>
       </c>
       <c r="F8">
-        <v>44.91068064068683</v>
+        <v>52.3957940808013</v>
       </c>
       <c r="G8">
         <v>15.1</v>
@@ -2443,28 +2443,28 @@
         <v>27.071</v>
       </c>
       <c r="M8">
-        <v>2.326373257187578</v>
+        <v>2.714102133385508</v>
       </c>
       <c r="N8">
-        <v>24.74462674281242</v>
+        <v>24.35689786661449</v>
       </c>
       <c r="O8">
-        <v>4.948925348562485</v>
+        <v>4.871379573322898</v>
       </c>
       <c r="P8">
-        <v>19.79570139424994</v>
+        <v>19.48551829329159</v>
       </c>
       <c r="Q8">
-        <v>25.53570139424994</v>
+        <v>25.22551829329159</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09897191632811474</v>
+        <v>0.09943486453522905</v>
       </c>
       <c r="T8">
-        <v>1.093270564117645</v>
+        <v>1.102789266517346</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.63656774181067</v>
+        <v>9.974200921552006</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2489,22 +2489,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09537522401776301</v>
+        <v>0.09533924668709817</v>
       </c>
       <c r="C9">
-        <v>708.3138519181213</v>
+        <v>701.3702292469407</v>
       </c>
       <c r="D9">
-        <v>745.6096459989226</v>
+        <v>746.1511367678564</v>
       </c>
       <c r="E9">
-        <v>35.78445006935409</v>
+        <v>43.26956350946856</v>
       </c>
       <c r="F9">
-        <v>52.39579408080131</v>
+        <v>59.88090752091578</v>
       </c>
       <c r="G9">
         <v>15.1</v>
@@ -2525,45 +2525,45 @@
         <v>27.071</v>
       </c>
       <c r="M9">
-        <v>2.714102133385508</v>
+        <v>3.203628552368994</v>
       </c>
       <c r="N9">
-        <v>24.35689786661449</v>
+        <v>23.867371447631</v>
       </c>
       <c r="O9">
-        <v>4.871379573322898</v>
+        <v>4.773474289526201</v>
       </c>
       <c r="P9">
-        <v>19.48551829329159</v>
+        <v>19.0938971581048</v>
       </c>
       <c r="Q9">
-        <v>25.22551829329159</v>
+        <v>24.8338971581048</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09943486453522905</v>
+        <v>0.09990787683380237</v>
       </c>
       <c r="T9">
-        <v>1.102789266517346</v>
+        <v>1.112514897230084</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.974200921552006</v>
+        <v>8.450105734006442</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2571,22 +2571,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09533924668709817</v>
+        <v>0.09526566935643334</v>
       </c>
       <c r="C10">
-        <v>701.3702292469407</v>
+        <v>694.994972594982</v>
       </c>
       <c r="D10">
-        <v>746.1511367678564</v>
+        <v>747.2609935560122</v>
       </c>
       <c r="E10">
-        <v>43.26956350946856</v>
+        <v>50.75467694958302</v>
       </c>
       <c r="F10">
-        <v>59.88090752091578</v>
+        <v>67.36602096103024</v>
       </c>
       <c r="G10">
         <v>15.1</v>
@@ -2607,45 +2607,45 @@
         <v>27.071</v>
       </c>
       <c r="M10">
-        <v>3.203628552368994</v>
+        <v>3.657974938183942</v>
       </c>
       <c r="N10">
-        <v>23.867371447631</v>
+        <v>23.41302506181606</v>
       </c>
       <c r="O10">
-        <v>4.773474289526201</v>
+        <v>4.682605012363211</v>
       </c>
       <c r="P10">
-        <v>19.0938971581048</v>
+        <v>18.73042004945285</v>
       </c>
       <c r="Q10">
-        <v>24.8338971581048</v>
+        <v>24.47042004945285</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09990787683380237</v>
+        <v>0.1003912850070696</v>
       </c>
       <c r="T10">
-        <v>1.112514897230084</v>
+        <v>1.122454278068376</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.450105734006442</v>
+        <v>7.400542775025083</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09526566935643334</v>
+        <v>0.09514089202576853</v>
       </c>
       <c r="C11">
-        <v>694.994972594982</v>
+        <v>689.3995945904805</v>
       </c>
       <c r="D11">
-        <v>747.2609935560122</v>
+        <v>749.1507289916252</v>
       </c>
       <c r="E11">
-        <v>50.75467694958302</v>
+        <v>58.2397903896975</v>
       </c>
       <c r="F11">
-        <v>67.36602096103024</v>
+        <v>74.85113440114472</v>
       </c>
       <c r="G11">
         <v>15.1</v>
@@ -2689,28 +2689,28 @@
         <v>27.071</v>
       </c>
       <c r="M11">
-        <v>3.657974938183942</v>
+        <v>4.064416597982158</v>
       </c>
       <c r="N11">
-        <v>23.41302506181606</v>
+        <v>23.00658340201784</v>
       </c>
       <c r="O11">
-        <v>4.682605012363211</v>
+        <v>4.601316680403568</v>
       </c>
       <c r="P11">
-        <v>18.73042004945285</v>
+        <v>18.40526672161427</v>
       </c>
       <c r="Q11">
-        <v>24.47042004945285</v>
+        <v>24.14526672161427</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1003912850070696</v>
+        <v>0.1008854355841872</v>
       </c>
       <c r="T11">
-        <v>1.122454278068376</v>
+        <v>1.132614534036409</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.400542775025083</v>
+        <v>6.660488497522573</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2735,22 +2735,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09514089202576853</v>
+        <v>0.09510411469510369</v>
       </c>
       <c r="C12">
-        <v>689.3995945904805</v>
+        <v>682.4732938224588</v>
       </c>
       <c r="D12">
-        <v>749.1507289916252</v>
+        <v>749.7095416637179</v>
       </c>
       <c r="E12">
-        <v>58.23979038969751</v>
+        <v>65.72490382981198</v>
       </c>
       <c r="F12">
-        <v>74.85113440114473</v>
+        <v>82.33624784125919</v>
       </c>
       <c r="G12">
         <v>15.1</v>
@@ -2771,45 +2771,45 @@
         <v>27.071</v>
       </c>
       <c r="M12">
-        <v>4.064416597982159</v>
+        <v>4.553194505621634</v>
       </c>
       <c r="N12">
-        <v>23.00658340201784</v>
+        <v>22.51780549437836</v>
       </c>
       <c r="O12">
-        <v>4.601316680403568</v>
+        <v>4.503561098875673</v>
       </c>
       <c r="P12">
-        <v>18.40526672161427</v>
+        <v>18.01424439550269</v>
       </c>
       <c r="Q12">
-        <v>24.14526672161427</v>
+        <v>23.7542443955027</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1008854355841872</v>
+        <v>0.1013906906686558</v>
       </c>
       <c r="T12">
-        <v>1.132614534036409</v>
+        <v>1.143003110363273</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.660488497522572</v>
+        <v>5.945496061408446</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2817,22 +2817,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09510411469510369</v>
+        <v>0.09498733736443885</v>
       </c>
       <c r="C13">
-        <v>682.4732938224588</v>
+        <v>676.7680913053686</v>
       </c>
       <c r="D13">
-        <v>749.7095416637179</v>
+        <v>751.4894525867422</v>
       </c>
       <c r="E13">
-        <v>65.72490382981198</v>
+        <v>73.21001726992645</v>
       </c>
       <c r="F13">
-        <v>82.33624784125919</v>
+        <v>89.82136128137367</v>
       </c>
       <c r="G13">
         <v>15.1</v>
@@ -2853,28 +2853,28 @@
         <v>27.071</v>
       </c>
       <c r="M13">
-        <v>4.553194505621634</v>
+        <v>4.967121278859964</v>
       </c>
       <c r="N13">
-        <v>22.51780549437836</v>
+        <v>22.10387872114003</v>
       </c>
       <c r="O13">
-        <v>4.503561098875673</v>
+        <v>4.420775744228007</v>
       </c>
       <c r="P13">
-        <v>18.01424439550269</v>
+        <v>17.68310297691203</v>
       </c>
       <c r="Q13">
-        <v>23.7542443955027</v>
+        <v>23.42310297691203</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1013906906686558</v>
+        <v>0.101907428823226</v>
       </c>
       <c r="T13">
-        <v>1.143003110363273</v>
+        <v>1.153627790697567</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.945496061408446</v>
+        <v>5.450038056291075</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2899,22 +2899,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09498733736443885</v>
+        <v>0.09487056003377402</v>
       </c>
       <c r="C14">
-        <v>676.7680913053686</v>
+        <v>671.0713603951347</v>
       </c>
       <c r="D14">
-        <v>751.4894525867422</v>
+        <v>753.2778351166228</v>
       </c>
       <c r="E14">
-        <v>73.21001726992645</v>
+        <v>80.69513071004093</v>
       </c>
       <c r="F14">
-        <v>89.82136128137367</v>
+        <v>97.30647472148814</v>
       </c>
       <c r="G14">
         <v>15.1</v>
@@ -2935,28 +2935,28 @@
         <v>27.071</v>
       </c>
       <c r="M14">
-        <v>4.967121278859964</v>
+        <v>5.381048052098294</v>
       </c>
       <c r="N14">
-        <v>22.10387872114003</v>
+        <v>21.6899519479017</v>
       </c>
       <c r="O14">
-        <v>4.420775744228007</v>
+        <v>4.337990389580341</v>
       </c>
       <c r="P14">
-        <v>17.68310297691203</v>
+        <v>17.35196155832136</v>
       </c>
       <c r="Q14">
-        <v>23.42310297691203</v>
+        <v>23.09196155832137</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.101907428823226</v>
+        <v>0.1024360460158322</v>
       </c>
       <c r="T14">
-        <v>1.153627790697567</v>
+        <v>1.164496716556786</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.450038056291075</v>
+        <v>5.0308043596533</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2981,22 +2981,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09487056003377402</v>
+        <v>0.09475378270310919</v>
       </c>
       <c r="C15">
-        <v>671.0713603951347</v>
+        <v>665.3831617178157</v>
       </c>
       <c r="D15">
-        <v>753.2778351166228</v>
+        <v>755.0747498794183</v>
       </c>
       <c r="E15">
-        <v>80.69513071004093</v>
+        <v>88.1802441501554</v>
       </c>
       <c r="F15">
-        <v>97.30647472148814</v>
+        <v>104.7915881616026</v>
       </c>
       <c r="G15">
         <v>15.1</v>
@@ -3017,28 +3017,28 @@
         <v>27.071</v>
       </c>
       <c r="M15">
-        <v>5.381048052098294</v>
+        <v>5.794974825336625</v>
       </c>
       <c r="N15">
-        <v>21.6899519479017</v>
+        <v>21.27602517466337</v>
       </c>
       <c r="O15">
-        <v>4.337990389580341</v>
+        <v>4.255205034932675</v>
       </c>
       <c r="P15">
-        <v>17.35196155832136</v>
+        <v>17.0208201397307</v>
       </c>
       <c r="Q15">
-        <v>23.09196155832137</v>
+        <v>22.7608201397307</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1024360460158322</v>
+        <v>0.1029769566315223</v>
       </c>
       <c r="T15">
-        <v>1.164496716556786</v>
+        <v>1.175618408133662</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.0308043596533</v>
+        <v>4.671461191106636</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3063,22 +3063,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09475378270310919</v>
+        <v>0.09493700537244433</v>
       </c>
       <c r="C16">
-        <v>665.3831617178157</v>
+        <v>655.0825162734237</v>
       </c>
       <c r="D16">
-        <v>755.0747498794183</v>
+        <v>752.2592178751408</v>
       </c>
       <c r="E16">
-        <v>88.1802441501554</v>
+        <v>95.66535759026988</v>
       </c>
       <c r="F16">
-        <v>104.7915881616026</v>
+        <v>112.2767016017171</v>
       </c>
       <c r="G16">
         <v>15.1</v>
@@ -3099,45 +3099,45 @@
         <v>27.071</v>
       </c>
       <c r="M16">
-        <v>5.794974825336625</v>
+        <v>6.48959335257925</v>
       </c>
       <c r="N16">
-        <v>21.27602517466337</v>
+        <v>20.58140664742075</v>
       </c>
       <c r="O16">
-        <v>4.255205034932675</v>
+        <v>4.11628132948415</v>
       </c>
       <c r="P16">
-        <v>17.0208201397307</v>
+        <v>16.4651253179366</v>
       </c>
       <c r="Q16">
-        <v>22.7608201397307</v>
+        <v>22.2051253179366</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1029769566315223</v>
+        <v>0.1035305945558169</v>
       </c>
       <c r="T16">
-        <v>1.175618408133662</v>
+        <v>1.18700178657117</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.671461191106636</v>
+        <v>4.171447813327285</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3145,22 +3145,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09493700537244433</v>
+        <v>0.09528822804177951</v>
       </c>
       <c r="C17">
-        <v>655.0825162734238</v>
+        <v>642.2585474935898</v>
       </c>
       <c r="D17">
-        <v>752.2592178751408</v>
+        <v>746.9203625354214</v>
       </c>
       <c r="E17">
-        <v>95.66535759026985</v>
+        <v>103.1504710303844</v>
       </c>
       <c r="F17">
-        <v>112.2767016017171</v>
+        <v>119.7618150418316</v>
       </c>
       <c r="G17">
         <v>15.1</v>
@@ -3181,45 +3181,45 @@
         <v>27.071</v>
       </c>
       <c r="M17">
-        <v>6.489593352579248</v>
+        <v>7.341399262064275</v>
       </c>
       <c r="N17">
-        <v>20.58140664742075</v>
+        <v>19.72960073793572</v>
       </c>
       <c r="O17">
-        <v>4.11628132948415</v>
+        <v>3.945920147587145</v>
       </c>
       <c r="P17">
-        <v>16.4651253179366</v>
+        <v>15.78368059034858</v>
       </c>
       <c r="Q17">
-        <v>22.2051253179366</v>
+        <v>21.52368059034858</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1035305945558169</v>
+        <v>0.1040974143354518</v>
       </c>
       <c r="T17">
-        <v>1.18700178657117</v>
+        <v>1.198656197828619</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.171447813327287</v>
+        <v>3.68744418245795</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3227,22 +3227,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09528822804177951</v>
+        <v>0.09560025071111469</v>
       </c>
       <c r="C18">
-        <v>642.2585474935898</v>
+        <v>630.0936165430971</v>
       </c>
       <c r="D18">
-        <v>746.9203625354214</v>
+        <v>742.2405450250432</v>
       </c>
       <c r="E18">
-        <v>103.1504710303844</v>
+        <v>110.6355844704988</v>
       </c>
       <c r="F18">
-        <v>119.7618150418316</v>
+        <v>127.246928481946</v>
       </c>
       <c r="G18">
         <v>15.1</v>
@@ -3263,45 +3263,45 @@
         <v>27.071</v>
       </c>
       <c r="M18">
-        <v>7.341399262064275</v>
+        <v>8.156528115692742</v>
       </c>
       <c r="N18">
-        <v>19.72960073793572</v>
+        <v>18.91447188430725</v>
       </c>
       <c r="O18">
-        <v>3.945920147587145</v>
+        <v>3.782894376861451</v>
       </c>
       <c r="P18">
-        <v>15.78368059034858</v>
+        <v>15.1315775074458</v>
       </c>
       <c r="Q18">
-        <v>21.52368059034858</v>
+        <v>20.8715775074458</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1040974143354518</v>
+        <v>0.1046778924230297</v>
       </c>
       <c r="T18">
-        <v>1.198656197828619</v>
+        <v>1.210591438272995</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.68744418245795</v>
+        <v>3.318936637748698</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3309,22 +3309,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09560025071111469</v>
+        <v>0.09555387338044984</v>
       </c>
       <c r="C19">
-        <v>630.0936165430971</v>
+        <v>623.3003715516213</v>
       </c>
       <c r="D19">
-        <v>742.2405450250432</v>
+        <v>742.9324134736818</v>
       </c>
       <c r="E19">
-        <v>110.6355844704988</v>
+        <v>118.1206979106133</v>
       </c>
       <c r="F19">
-        <v>127.246928481946</v>
+        <v>134.7320419220605</v>
       </c>
       <c r="G19">
         <v>15.1</v>
@@ -3345,28 +3345,28 @@
         <v>27.071</v>
       </c>
       <c r="M19">
-        <v>8.156528115692742</v>
+        <v>8.63632388720408</v>
       </c>
       <c r="N19">
-        <v>18.91447188430725</v>
+        <v>18.43467611279592</v>
       </c>
       <c r="O19">
-        <v>3.782894376861451</v>
+        <v>3.686935222559184</v>
       </c>
       <c r="P19">
-        <v>15.1315775074458</v>
+        <v>14.74774089023674</v>
       </c>
       <c r="Q19">
-        <v>20.8715775074458</v>
+        <v>20.48774089023674</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1046778924230297</v>
+        <v>0.1052725285127437</v>
       </c>
       <c r="T19">
-        <v>1.210591438272995</v>
+        <v>1.222817782142843</v>
       </c>
       <c r="U19">
         <v>0.0641</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.318936637748698</v>
+        <v>3.134551268984882</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3391,22 +3391,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09555387338044985</v>
+        <v>0.09669309604978503</v>
       </c>
       <c r="C20">
-        <v>623.300371551621</v>
+        <v>599.1849975672242</v>
       </c>
       <c r="D20">
-        <v>742.9324134736814</v>
+        <v>726.3021529293991</v>
       </c>
       <c r="E20">
-        <v>118.1206979106133</v>
+        <v>125.6058113507278</v>
       </c>
       <c r="F20">
-        <v>134.7320419220605</v>
+        <v>142.217155362175</v>
       </c>
       <c r="G20">
         <v>15.1</v>
@@ -3427,45 +3427,45 @@
         <v>27.071</v>
       </c>
       <c r="M20">
-        <v>8.636323887204078</v>
+        <v>10.22541347054038</v>
       </c>
       <c r="N20">
-        <v>18.43467611279592</v>
+        <v>16.84558652945962</v>
       </c>
       <c r="O20">
-        <v>3.686935222559184</v>
+        <v>3.369117305891923</v>
       </c>
       <c r="P20">
-        <v>14.74774089023674</v>
+        <v>13.47646922356769</v>
       </c>
       <c r="Q20">
-        <v>20.48774089023674</v>
+        <v>19.21646922356769</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1052725285127437</v>
+        <v>0.1058818469750432</v>
       </c>
       <c r="T20">
-        <v>1.222817782142843</v>
+        <v>1.235346011046514</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.134551268984882</v>
+        <v>2.647423507909199</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3473,22 +3473,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09669309604978503</v>
+        <v>0.09670911871912018</v>
       </c>
       <c r="C21">
-        <v>599.1849975672242</v>
+        <v>591.4712944456029</v>
       </c>
       <c r="D21">
-        <v>726.3021529293991</v>
+        <v>726.0735632478924</v>
       </c>
       <c r="E21">
-        <v>125.6058113507278</v>
+        <v>133.0909247908423</v>
       </c>
       <c r="F21">
-        <v>142.217155362175</v>
+        <v>149.7022688022895</v>
       </c>
       <c r="G21">
         <v>15.1</v>
@@ -3509,28 +3509,28 @@
         <v>27.071</v>
       </c>
       <c r="M21">
-        <v>10.22541347054038</v>
+        <v>10.76359312688461</v>
       </c>
       <c r="N21">
-        <v>16.84558652945962</v>
+        <v>16.30740687311538</v>
       </c>
       <c r="O21">
-        <v>3.369117305891923</v>
+        <v>3.261481374623077</v>
       </c>
       <c r="P21">
-        <v>13.47646922356769</v>
+        <v>13.04592549849231</v>
       </c>
       <c r="Q21">
-        <v>19.21646922356769</v>
+        <v>18.7859254984923</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1058818469750432</v>
+        <v>0.1065063983989002</v>
       </c>
       <c r="T21">
-        <v>1.235346011046514</v>
+        <v>1.248187445672777</v>
       </c>
       <c r="U21">
         <v>0.07190000000000001</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.647423507909199</v>
+        <v>2.515052332513739</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3555,22 +3555,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09670911871912018</v>
+        <v>0.09738034138845536</v>
       </c>
       <c r="C22">
-        <v>591.4712944456029</v>
+        <v>574.5376775226084</v>
       </c>
       <c r="D22">
-        <v>726.0735632478924</v>
+        <v>716.6250597650123</v>
       </c>
       <c r="E22">
-        <v>133.0909247908423</v>
+        <v>140.5760382309567</v>
       </c>
       <c r="F22">
-        <v>149.7022688022895</v>
+        <v>157.1873822424039</v>
       </c>
       <c r="G22">
         <v>15.1</v>
@@ -3591,45 +3591,45 @@
         <v>27.071</v>
       </c>
       <c r="M22">
-        <v>10.76359312688461</v>
+        <v>11.91480357397422</v>
       </c>
       <c r="N22">
-        <v>16.30740687311538</v>
+        <v>15.15619642602578</v>
       </c>
       <c r="O22">
-        <v>3.261481374623077</v>
+        <v>3.031239285205156</v>
       </c>
       <c r="P22">
-        <v>13.04592549849231</v>
+        <v>12.12495714082062</v>
       </c>
       <c r="Q22">
-        <v>18.7859254984923</v>
+        <v>17.86495714082062</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1065063983989002</v>
+        <v>0.1071467612512093</v>
       </c>
       <c r="T22">
-        <v>1.248187445672777</v>
+        <v>1.261353979909832</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.515052332513739</v>
+        <v>2.272047527424775</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3637,22 +3637,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09738034138845536</v>
+        <v>0.09742756405779052</v>
       </c>
       <c r="C23">
-        <v>574.5376775226084</v>
+        <v>566.3970819025351</v>
       </c>
       <c r="D23">
-        <v>716.6250597650123</v>
+        <v>715.9695775850535</v>
       </c>
       <c r="E23">
-        <v>140.5760382309567</v>
+        <v>148.0611516710712</v>
       </c>
       <c r="F23">
-        <v>157.1873822424039</v>
+        <v>164.6724956825184</v>
       </c>
       <c r="G23">
         <v>15.1</v>
@@ -3673,28 +3673,28 @@
         <v>27.071</v>
       </c>
       <c r="M23">
-        <v>11.91480357397422</v>
+        <v>12.48217517273489</v>
       </c>
       <c r="N23">
-        <v>15.15619642602578</v>
+        <v>14.5888248272651</v>
       </c>
       <c r="O23">
-        <v>3.031239285205156</v>
+        <v>2.917764965453021</v>
       </c>
       <c r="P23">
-        <v>12.12495714082062</v>
+        <v>11.67105986181208</v>
       </c>
       <c r="Q23">
-        <v>17.86495714082062</v>
+        <v>17.41105986181208</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1071467612512093</v>
+        <v>0.107803543663834</v>
       </c>
       <c r="T23">
-        <v>1.261353979909832</v>
+        <v>1.274858117588862</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.272047527424776</v>
+        <v>2.168772639814558</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09742756405779052</v>
+        <v>0.09747478672712569</v>
       </c>
       <c r="C24">
-        <v>566.3970819025351</v>
+        <v>558.2576842987553</v>
       </c>
       <c r="D24">
-        <v>715.9695775850535</v>
+        <v>715.3152934213881</v>
       </c>
       <c r="E24">
-        <v>148.0611516710712</v>
+        <v>155.5462651111856</v>
       </c>
       <c r="F24">
-        <v>164.6724956825184</v>
+        <v>172.1576091226329</v>
       </c>
       <c r="G24">
         <v>15.1</v>
@@ -3755,28 +3755,28 @@
         <v>27.071</v>
       </c>
       <c r="M24">
-        <v>12.48217517273489</v>
+        <v>13.04954677149557</v>
       </c>
       <c r="N24">
-        <v>14.5888248272651</v>
+        <v>14.02145322850443</v>
       </c>
       <c r="O24">
-        <v>2.917764965453021</v>
+        <v>2.804290645700885</v>
       </c>
       <c r="P24">
-        <v>11.67105986181208</v>
+        <v>11.21716258280354</v>
       </c>
       <c r="Q24">
-        <v>17.41105986181208</v>
+        <v>16.95716258280354</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.107803543663834</v>
+        <v>0.1084773853599035</v>
       </c>
       <c r="T24">
-        <v>1.274858117588862</v>
+        <v>1.288713012090725</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.168772639814558</v>
+        <v>2.074478177213925</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3801,22 +3801,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09747478672712569</v>
+        <v>0.1002484093964608</v>
       </c>
       <c r="C25">
-        <v>558.2576842987553</v>
+        <v>514.3341379356644</v>
       </c>
       <c r="D25">
-        <v>715.3152934213881</v>
+        <v>678.8768604984118</v>
       </c>
       <c r="E25">
-        <v>155.5462651111856</v>
+        <v>163.0313785513002</v>
       </c>
       <c r="F25">
-        <v>172.1576091226329</v>
+        <v>179.6427225627474</v>
       </c>
       <c r="G25">
         <v>15.1</v>
@@ -3837,45 +3837,45 @@
         <v>27.071</v>
       </c>
       <c r="M25">
-        <v>13.04954677149557</v>
+        <v>16.16784503064726</v>
       </c>
       <c r="N25">
-        <v>14.02145322850443</v>
+        <v>10.90315496935273</v>
       </c>
       <c r="O25">
-        <v>2.804290645700885</v>
+        <v>2.180630993870547</v>
       </c>
       <c r="P25">
-        <v>11.21716258280354</v>
+        <v>8.722523975482186</v>
       </c>
       <c r="Q25">
-        <v>16.95716258280354</v>
+        <v>14.46252397548219</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1084773853599035</v>
+        <v>0.1091689597321853</v>
       </c>
       <c r="T25">
-        <v>1.288713012090725</v>
+        <v>1.302932509079478</v>
       </c>
       <c r="U25">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.074478177213925</v>
+        <v>1.674372802849424</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3883,22 +3883,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1002484093964608</v>
+        <v>0.100409232065796</v>
       </c>
       <c r="C26">
-        <v>514.3341379356646</v>
+        <v>504.8497510261175</v>
       </c>
       <c r="D26">
-        <v>678.8768604984118</v>
+        <v>676.8775870289793</v>
       </c>
       <c r="E26">
-        <v>163.0313785513001</v>
+        <v>170.5164919914146</v>
       </c>
       <c r="F26">
-        <v>179.6427225627473</v>
+        <v>187.1278360028618</v>
       </c>
       <c r="G26">
         <v>15.1</v>
@@ -3919,28 +3919,28 @@
         <v>27.071</v>
       </c>
       <c r="M26">
-        <v>16.16784503064726</v>
+        <v>16.84150524025756</v>
       </c>
       <c r="N26">
-        <v>10.90315496935274</v>
+        <v>10.22949475974244</v>
       </c>
       <c r="O26">
-        <v>2.180630993870547</v>
+        <v>2.045898951948487</v>
       </c>
       <c r="P26">
-        <v>8.72252397548219</v>
+        <v>8.183595807793949</v>
       </c>
       <c r="Q26">
-        <v>14.46252397548219</v>
+        <v>13.92359580779395</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1091689597321853</v>
+        <v>0.109878976087728</v>
       </c>
       <c r="T26">
-        <v>1.302932509079478</v>
+        <v>1.317531192654598</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.674372802849425</v>
+        <v>1.607397890735448</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3965,22 +3965,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.100409232065796</v>
+        <v>0.1005700547351312</v>
       </c>
       <c r="C27">
-        <v>504.8497510261175</v>
+        <v>495.3771051490612</v>
       </c>
       <c r="D27">
-        <v>676.8775870289793</v>
+        <v>674.8900545920375</v>
       </c>
       <c r="E27">
-        <v>170.5164919914146</v>
+        <v>178.0016054315291</v>
       </c>
       <c r="F27">
-        <v>187.1278360028618</v>
+        <v>194.6129494429763</v>
       </c>
       <c r="G27">
         <v>15.1</v>
@@ -4001,28 +4001,28 @@
         <v>27.071</v>
       </c>
       <c r="M27">
-        <v>16.84150524025756</v>
+        <v>17.51516544986787</v>
       </c>
       <c r="N27">
-        <v>10.22949475974244</v>
+        <v>9.555834550132133</v>
       </c>
       <c r="O27">
-        <v>2.045898951948487</v>
+        <v>1.911166910026427</v>
       </c>
       <c r="P27">
-        <v>8.183595807793949</v>
+        <v>7.644667640105706</v>
       </c>
       <c r="Q27">
-        <v>13.92359580779395</v>
+        <v>13.38466764010571</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.109878976087728</v>
+        <v>0.1106081820745016</v>
       </c>
       <c r="T27">
-        <v>1.317531192654598</v>
+        <v>1.332524435245262</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.607397890735448</v>
+        <v>1.545574894937931</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4047,22 +4047,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1005700547351312</v>
+        <v>0.1139327146553266</v>
       </c>
       <c r="C28">
-        <v>495.3771051490612</v>
+        <v>355.5278795690166</v>
       </c>
       <c r="D28">
-        <v>674.8900545920375</v>
+        <v>542.5259424521073</v>
       </c>
       <c r="E28">
-        <v>178.0016054315291</v>
+        <v>185.4867188716435</v>
       </c>
       <c r="F28">
-        <v>194.6129494429763</v>
+        <v>202.0980628830908</v>
       </c>
       <c r="G28">
         <v>15.1</v>
@@ -4083,45 +4083,45 @@
         <v>27.071</v>
       </c>
       <c r="M28">
-        <v>17.51516544986787</v>
+        <v>29.66799563123773</v>
       </c>
       <c r="N28">
-        <v>9.555834550132133</v>
+        <v>-2.596995631237728</v>
       </c>
       <c r="O28">
-        <v>1.911166910026427</v>
+        <v>-0.5193991262475457</v>
       </c>
       <c r="P28">
-        <v>7.644667640105706</v>
+        <v>-2.077596504990183</v>
       </c>
       <c r="Q28">
-        <v>13.38466764010571</v>
+        <v>3.662403495009817</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1106081820745016</v>
+        <v>0.1116849385803234</v>
       </c>
       <c r="T28">
-        <v>1.332524435245262</v>
+        <v>1.354663682310817</v>
       </c>
       <c r="U28">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.2</v>
+        <v>0.1824929485394468</v>
       </c>
       <c r="W28">
-        <v>0.07199999999999999</v>
+        <v>0.1200100351544092</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.545574894937931</v>
+        <v>0.9124647426972341</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4129,22 +4129,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1139327146553266</v>
+        <v>0.1149427146553266</v>
       </c>
       <c r="C29">
-        <v>355.5278795690166</v>
+        <v>340.1178357207147</v>
       </c>
       <c r="D29">
-        <v>542.5259424521073</v>
+        <v>534.6010120439199</v>
       </c>
       <c r="E29">
-        <v>185.4867188716435</v>
+        <v>192.971832311758</v>
       </c>
       <c r="F29">
-        <v>202.0980628830908</v>
+        <v>209.5831763232052</v>
       </c>
       <c r="G29">
         <v>15.1</v>
@@ -4165,37 +4165,37 @@
         <v>27.071</v>
       </c>
       <c r="M29">
-        <v>29.66799563123773</v>
+        <v>30.76681028424653</v>
       </c>
       <c r="N29">
-        <v>-2.596995631237728</v>
+        <v>-3.695810284246534</v>
       </c>
       <c r="O29">
-        <v>-0.5193991262475457</v>
+        <v>-0.7391620568493068</v>
       </c>
       <c r="P29">
-        <v>-2.077596504990183</v>
+        <v>-2.956648227397227</v>
       </c>
       <c r="Q29">
-        <v>3.662403495009817</v>
+        <v>2.783351772602773</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1116849385803234</v>
+        <v>0.1126000071717168</v>
       </c>
       <c r="T29">
-        <v>1.354663682310817</v>
+        <v>1.373478455676245</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.1824929485394468</v>
+        <v>0.1759753432344666</v>
       </c>
       <c r="W29">
-        <v>0.1200100351544092</v>
+        <v>0.1209668196131803</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.9124647426972341</v>
+        <v>0.8798767161723329</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4211,22 +4211,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1149427146553266</v>
+        <v>0.1159527146553266</v>
       </c>
       <c r="C30">
-        <v>340.1178357207147</v>
+        <v>324.9359848867983</v>
       </c>
       <c r="D30">
-        <v>534.6010120439199</v>
+        <v>526.9042746501181</v>
       </c>
       <c r="E30">
-        <v>192.971832311758</v>
+        <v>200.4569457518725</v>
       </c>
       <c r="F30">
-        <v>209.5831763232052</v>
+        <v>217.0682897633197</v>
       </c>
       <c r="G30">
         <v>15.1</v>
@@ -4247,37 +4247,37 @@
         <v>27.071</v>
       </c>
       <c r="M30">
-        <v>30.76681028424653</v>
+        <v>31.86562493725534</v>
       </c>
       <c r="N30">
-        <v>-3.695810284246534</v>
+        <v>-4.794624937255342</v>
       </c>
       <c r="O30">
-        <v>-0.7391620568493068</v>
+        <v>-0.9589249874510686</v>
       </c>
       <c r="P30">
-        <v>-2.956648227397227</v>
+        <v>-3.835699949804274</v>
       </c>
       <c r="Q30">
-        <v>2.783351772602773</v>
+        <v>1.904300050195726</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1126000071717168</v>
+        <v>0.1135408523431494</v>
       </c>
       <c r="T30">
-        <v>1.373478455676245</v>
+        <v>1.392823222657601</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.1759753432344666</v>
+        <v>0.1699072279505194</v>
       </c>
       <c r="W30">
-        <v>0.1209668196131803</v>
+        <v>0.1218576189368638</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8798767161723329</v>
+        <v>0.8495361397525971</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4293,22 +4293,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1159527146553266</v>
+        <v>0.1169627146553266</v>
       </c>
       <c r="C31">
-        <v>324.9359848867984</v>
+        <v>309.9726109562829</v>
       </c>
       <c r="D31">
-        <v>526.9042746501181</v>
+        <v>519.4260141597171</v>
       </c>
       <c r="E31">
-        <v>200.4569457518725</v>
+        <v>207.9420591919869</v>
       </c>
       <c r="F31">
-        <v>217.0682897633197</v>
+        <v>224.5534032034342</v>
       </c>
       <c r="G31">
         <v>15.1</v>
@@ -4329,37 +4329,37 @@
         <v>27.071</v>
       </c>
       <c r="M31">
-        <v>31.86562493725533</v>
+        <v>32.96443959026413</v>
       </c>
       <c r="N31">
-        <v>-4.794624937255335</v>
+        <v>-5.893439590264137</v>
       </c>
       <c r="O31">
-        <v>-0.9589249874510671</v>
+        <v>-1.178687918052827</v>
       </c>
       <c r="P31">
-        <v>-3.835699949804268</v>
+        <v>-4.714751672211309</v>
       </c>
       <c r="Q31">
-        <v>1.904300050195732</v>
+        <v>1.025248327788691</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1135408523431494</v>
+        <v>0.1145085788051944</v>
       </c>
       <c r="T31">
-        <v>1.392823222657601</v>
+        <v>1.412720697266995</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.1699072279505195</v>
+        <v>0.1642436536855022</v>
       </c>
       <c r="W31">
-        <v>0.1218576189368638</v>
+        <v>0.1226890316389683</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8495361397525973</v>
+        <v>0.8212182684275109</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4375,22 +4375,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1169627146553266</v>
+        <v>0.1353830515533055</v>
       </c>
       <c r="C32">
-        <v>309.9726109562829</v>
+        <v>195.6815558955818</v>
       </c>
       <c r="D32">
-        <v>519.4260141597171</v>
+        <v>412.6200725391304</v>
       </c>
       <c r="E32">
-        <v>207.9420591919869</v>
+        <v>215.4271726321014</v>
       </c>
       <c r="F32">
-        <v>224.5534032034342</v>
+        <v>232.0385166435486</v>
       </c>
       <c r="G32">
         <v>15.1</v>
@@ -4411,45 +4411,45 @@
         <v>27.071</v>
       </c>
       <c r="M32">
-        <v>32.96443959026413</v>
+        <v>46.59333414202457</v>
       </c>
       <c r="N32">
-        <v>-5.893439590264137</v>
+        <v>-19.52233414202457</v>
       </c>
       <c r="O32">
-        <v>-1.178687918052827</v>
+        <v>-3.904466828404914</v>
       </c>
       <c r="P32">
-        <v>-4.714751672211309</v>
+        <v>-15.61786731361966</v>
       </c>
       <c r="Q32">
-        <v>1.025248327788691</v>
+        <v>-9.877867313619655</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1145085788051944</v>
+        <v>0.1164758580603116</v>
       </c>
       <c r="T32">
-        <v>1.412720697266995</v>
+        <v>1.453170029349496</v>
       </c>
       <c r="U32">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1642436536855022</v>
+        <v>0.1162011712554542</v>
       </c>
       <c r="W32">
-        <v>0.1226890316389683</v>
+        <v>0.1774668048119048</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.8212182684275109</v>
+        <v>0.5810058562772712</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4457,22 +4457,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1353830515533055</v>
+        <v>0.1369330515533054</v>
       </c>
       <c r="C33">
-        <v>195.6815558955818</v>
+        <v>181.178559244769</v>
       </c>
       <c r="D33">
-        <v>412.6200725391304</v>
+        <v>405.6021893284321</v>
       </c>
       <c r="E33">
-        <v>215.4271726321014</v>
+        <v>222.9122860722159</v>
       </c>
       <c r="F33">
-        <v>232.0385166435486</v>
+        <v>239.5236300836631</v>
       </c>
       <c r="G33">
         <v>15.1</v>
@@ -4493,37 +4493,37 @@
         <v>27.071</v>
       </c>
       <c r="M33">
-        <v>46.59333414202457</v>
+        <v>48.09634492079956</v>
       </c>
       <c r="N33">
-        <v>-19.52233414202457</v>
+        <v>-21.02534492079956</v>
       </c>
       <c r="O33">
-        <v>-3.904466828404914</v>
+        <v>-4.205068984159912</v>
       </c>
       <c r="P33">
-        <v>-15.61786731361966</v>
+        <v>-16.82027593663965</v>
       </c>
       <c r="Q33">
-        <v>-9.877867313619655</v>
+        <v>-11.08027593663965</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1164758580603116</v>
+        <v>0.1175152089141397</v>
       </c>
       <c r="T33">
-        <v>1.453170029349496</v>
+        <v>1.47454017683993</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1162011712554542</v>
+        <v>0.1125698846537213</v>
       </c>
       <c r="W33">
-        <v>0.1774668048119048</v>
+        <v>0.1781959671615328</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5810058562772712</v>
+        <v>0.5628494232686063</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4539,22 +4539,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1369330515533054</v>
+        <v>0.1384830515533055</v>
       </c>
       <c r="C34">
-        <v>181.178559244769</v>
+        <v>166.9102920033634</v>
       </c>
       <c r="D34">
-        <v>405.6021893284321</v>
+        <v>398.819035527141</v>
       </c>
       <c r="E34">
-        <v>222.9122860722159</v>
+        <v>230.3973995123304</v>
       </c>
       <c r="F34">
-        <v>239.5236300836631</v>
+        <v>247.0087435237776</v>
       </c>
       <c r="G34">
         <v>15.1</v>
@@ -4575,37 +4575,37 @@
         <v>27.071</v>
       </c>
       <c r="M34">
-        <v>48.09634492079956</v>
+        <v>49.59935569957455</v>
       </c>
       <c r="N34">
-        <v>-21.02534492079956</v>
+        <v>-22.52835569957455</v>
       </c>
       <c r="O34">
-        <v>-4.205068984159912</v>
+        <v>-4.505671139914909</v>
       </c>
       <c r="P34">
-        <v>-16.82027593663965</v>
+        <v>-18.02268455965964</v>
       </c>
       <c r="Q34">
-        <v>-11.08027593663965</v>
+        <v>-12.28268455965964</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1175152089141397</v>
+        <v>0.1185855851665895</v>
       </c>
       <c r="T34">
-        <v>1.47454017683993</v>
+        <v>1.496548239180824</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1125698846537213</v>
+        <v>0.109158676027851</v>
       </c>
       <c r="W34">
-        <v>0.1781959671615328</v>
+        <v>0.1788809378536075</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5628494232686063</v>
+        <v>0.5457933801392547</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4621,22 +4621,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1384830515533055</v>
+        <v>0.1400330515533055</v>
       </c>
       <c r="C35">
-        <v>166.9102920033634</v>
+        <v>152.8651712741143</v>
       </c>
       <c r="D35">
-        <v>398.819035527141</v>
+        <v>392.2590282380064</v>
       </c>
       <c r="E35">
-        <v>230.3973995123304</v>
+        <v>237.8825129524449</v>
       </c>
       <c r="F35">
-        <v>247.0087435237776</v>
+        <v>254.4938569638921</v>
       </c>
       <c r="G35">
         <v>15.1</v>
@@ -4657,37 +4657,37 @@
         <v>27.071</v>
       </c>
       <c r="M35">
-        <v>49.59935569957455</v>
+        <v>51.10236647834953</v>
       </c>
       <c r="N35">
-        <v>-22.52835569957455</v>
+        <v>-24.03136647834953</v>
       </c>
       <c r="O35">
-        <v>-4.505671139914909</v>
+        <v>-4.806273295669907</v>
       </c>
       <c r="P35">
-        <v>-18.02268455965964</v>
+        <v>-19.22509318267963</v>
       </c>
       <c r="Q35">
-        <v>-12.28268455965964</v>
+        <v>-13.48509318267963</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1185855851665895</v>
+        <v>0.119688397063053</v>
       </c>
       <c r="T35">
-        <v>1.496548239180824</v>
+        <v>1.519223212501746</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.109158676027851</v>
+        <v>0.1059481267329141</v>
       </c>
       <c r="W35">
-        <v>0.1788809378536075</v>
+        <v>0.1795256161520309</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5457933801392547</v>
+        <v>0.5297406336645707</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4703,22 +4703,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1400330515533055</v>
+        <v>0.1415830515533055</v>
       </c>
       <c r="C36">
-        <v>152.8651712741143</v>
+        <v>139.0323639162451</v>
       </c>
       <c r="D36">
-        <v>392.2590282380064</v>
+        <v>385.9113343202516</v>
       </c>
       <c r="E36">
-        <v>237.8825129524449</v>
+        <v>245.3676263925594</v>
       </c>
       <c r="F36">
-        <v>254.4938569638921</v>
+        <v>261.9789704040066</v>
       </c>
       <c r="G36">
         <v>15.1</v>
@@ -4739,37 +4739,37 @@
         <v>27.071</v>
       </c>
       <c r="M36">
-        <v>51.10236647834953</v>
+        <v>52.60537725712452</v>
       </c>
       <c r="N36">
-        <v>-24.03136647834953</v>
+        <v>-25.53437725712453</v>
       </c>
       <c r="O36">
-        <v>-4.806273295669907</v>
+        <v>-5.106875451424905</v>
       </c>
       <c r="P36">
-        <v>-19.22509318267963</v>
+        <v>-20.42750180569962</v>
       </c>
       <c r="Q36">
-        <v>-13.48509318267963</v>
+        <v>-14.68750180569962</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.119688397063053</v>
+        <v>0.1208251416332538</v>
       </c>
       <c r="T36">
-        <v>1.519223212501746</v>
+        <v>1.542595877309465</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1059481267329141</v>
+        <v>0.102921037397688</v>
       </c>
       <c r="W36">
-        <v>0.1795256161520309</v>
+        <v>0.1801334556905443</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5297406336645707</v>
+        <v>0.51460518698844</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1415830515533055</v>
+        <v>0.1431330515533055</v>
       </c>
       <c r="C37">
-        <v>139.0323639162451</v>
+        <v>125.4017268472038</v>
       </c>
       <c r="D37">
-        <v>385.9113343202516</v>
+        <v>379.7658106913248</v>
       </c>
       <c r="E37">
-        <v>245.3676263925594</v>
+        <v>252.8527398326738</v>
       </c>
       <c r="F37">
-        <v>261.9789704040066</v>
+        <v>269.464083844121</v>
       </c>
       <c r="G37">
         <v>15.1</v>
@@ -4821,37 +4821,37 @@
         <v>27.071</v>
       </c>
       <c r="M37">
-        <v>52.60537725712452</v>
+        <v>54.10838803589951</v>
       </c>
       <c r="N37">
-        <v>-25.53437725712453</v>
+        <v>-27.03738803589951</v>
       </c>
       <c r="O37">
-        <v>-5.106875451424905</v>
+        <v>-5.407477607179903</v>
       </c>
       <c r="P37">
-        <v>-20.42750180569962</v>
+        <v>-21.62991042871961</v>
       </c>
       <c r="Q37">
-        <v>-14.68750180569962</v>
+        <v>-15.88991042871961</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1208251416332538</v>
+        <v>0.1219974094712734</v>
       </c>
       <c r="T37">
-        <v>1.542595877309465</v>
+        <v>1.566698937892426</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.102921037397688</v>
+        <v>0.1000621196921967</v>
       </c>
       <c r="W37">
-        <v>0.1801334556905443</v>
+        <v>0.1807075263658069</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.51460518698844</v>
+        <v>0.5003105984609835</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4867,22 +4867,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1431330515533055</v>
+        <v>0.1579035405884117</v>
       </c>
       <c r="C38">
-        <v>125.4017268472039</v>
+        <v>67.87959661634312</v>
       </c>
       <c r="D38">
-        <v>379.7658106913248</v>
+        <v>329.7287939005786</v>
       </c>
       <c r="E38">
-        <v>252.8527398326738</v>
+        <v>260.3378532727883</v>
       </c>
       <c r="F38">
-        <v>269.464083844121</v>
+        <v>276.9491972842355</v>
       </c>
       <c r="G38">
         <v>15.1</v>
@@ -4903,45 +4903,45 @@
         <v>27.071</v>
       </c>
       <c r="M38">
-        <v>54.10838803589949</v>
+        <v>65.30462071962273</v>
       </c>
       <c r="N38">
-        <v>-27.0373880358995</v>
+        <v>-38.23362071962273</v>
       </c>
       <c r="O38">
-        <v>-5.407477607179899</v>
+        <v>-7.646724143924548</v>
       </c>
       <c r="P38">
-        <v>-21.6299104287196</v>
+        <v>-30.58689657569819</v>
       </c>
       <c r="Q38">
-        <v>-15.8899104287196</v>
+        <v>-24.84689657569819</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1219974094712734</v>
+        <v>0.1236362398360655</v>
       </c>
       <c r="T38">
-        <v>1.566698937892425</v>
+        <v>1.600395015091397</v>
       </c>
       <c r="U38">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.1000621196921967</v>
+        <v>0.08290684396200988</v>
       </c>
       <c r="W38">
-        <v>0.1807075263658069</v>
+        <v>0.2162505661937581</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.5003105984609835</v>
+        <v>0.4145342198100495</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4949,22 +4949,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1579035405884117</v>
+        <v>0.1598035405884118</v>
       </c>
       <c r="C39">
-        <v>67.87959661634312</v>
+        <v>54.89917395006239</v>
       </c>
       <c r="D39">
-        <v>329.7287939005786</v>
+        <v>324.2334846744124</v>
       </c>
       <c r="E39">
-        <v>260.3378532727883</v>
+        <v>267.8229667129028</v>
       </c>
       <c r="F39">
-        <v>276.9491972842355</v>
+        <v>284.43431072435</v>
       </c>
       <c r="G39">
         <v>15.1</v>
@@ -4985,37 +4985,37 @@
         <v>27.071</v>
       </c>
       <c r="M39">
-        <v>65.30462071962273</v>
+        <v>67.06961046880173</v>
       </c>
       <c r="N39">
-        <v>-38.23362071962273</v>
+        <v>-39.99861046880173</v>
       </c>
       <c r="O39">
-        <v>-7.646724143924548</v>
+        <v>-7.999722093760346</v>
       </c>
       <c r="P39">
-        <v>-30.58689657569819</v>
+        <v>-31.99888837504138</v>
       </c>
       <c r="Q39">
-        <v>-24.84689657569819</v>
+        <v>-26.25888837504138</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1236362398360655</v>
+        <v>0.1248916630592279</v>
       </c>
       <c r="T39">
-        <v>1.600395015091397</v>
+        <v>1.626207837915452</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.08290684396200988</v>
+        <v>0.08072508491037805</v>
       </c>
       <c r="W39">
-        <v>0.2162505661937581</v>
+        <v>0.2167650249781329</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4145342198100495</v>
+        <v>0.4036254245518902</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5031,22 +5031,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1598035405884118</v>
+        <v>0.1617035405884117</v>
       </c>
       <c r="C40">
-        <v>54.89917395006239</v>
+        <v>42.0989198528647</v>
       </c>
       <c r="D40">
-        <v>324.2334846744124</v>
+        <v>318.9183440173291</v>
       </c>
       <c r="E40">
-        <v>267.8229667129028</v>
+        <v>275.3080801530172</v>
       </c>
       <c r="F40">
-        <v>284.43431072435</v>
+        <v>291.9194241644644</v>
       </c>
       <c r="G40">
         <v>15.1</v>
@@ -5067,37 +5067,37 @@
         <v>27.071</v>
       </c>
       <c r="M40">
-        <v>67.06961046880173</v>
+        <v>68.83460021798072</v>
       </c>
       <c r="N40">
-        <v>-39.99861046880173</v>
+        <v>-41.76360021798072</v>
       </c>
       <c r="O40">
-        <v>-7.999722093760346</v>
+        <v>-8.352720043596145</v>
       </c>
       <c r="P40">
-        <v>-31.99888837504138</v>
+        <v>-33.41088017438458</v>
       </c>
       <c r="Q40">
-        <v>-26.25888837504138</v>
+        <v>-27.67088017438458</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1248916630592279</v>
+        <v>0.1261882476995431</v>
       </c>
       <c r="T40">
-        <v>1.626207837915452</v>
+        <v>1.652866982799311</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.08072508491037805</v>
+        <v>0.07865521093831707</v>
       </c>
       <c r="W40">
-        <v>0.2167650249781329</v>
+        <v>0.2172531012607448</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4036254245518902</v>
+        <v>0.3932760546915853</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5113,22 +5113,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1617035405884117</v>
+        <v>0.1636035405884118</v>
       </c>
       <c r="C41">
-        <v>42.0989198528647</v>
+        <v>29.47011675277628</v>
       </c>
       <c r="D41">
-        <v>318.9183440173291</v>
+        <v>313.7746543573552</v>
       </c>
       <c r="E41">
-        <v>275.3080801530172</v>
+        <v>282.7931935931317</v>
       </c>
       <c r="F41">
-        <v>291.9194241644644</v>
+        <v>299.4045376045789</v>
       </c>
       <c r="G41">
         <v>15.1</v>
@@ -5149,37 +5149,37 @@
         <v>27.071</v>
       </c>
       <c r="M41">
-        <v>68.83460021798072</v>
+        <v>70.59958996715972</v>
       </c>
       <c r="N41">
-        <v>-41.76360021798072</v>
+        <v>-43.52858996715972</v>
       </c>
       <c r="O41">
-        <v>-8.352720043596145</v>
+        <v>-8.705717993431945</v>
       </c>
       <c r="P41">
-        <v>-33.41088017438458</v>
+        <v>-34.82287197372777</v>
       </c>
       <c r="Q41">
-        <v>-27.67088017438458</v>
+        <v>-29.08287197372777</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1261882476995431</v>
+        <v>0.1275280518278688</v>
       </c>
       <c r="T41">
-        <v>1.652866982799311</v>
+        <v>1.680414765845967</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07865521093831707</v>
+        <v>0.07668883066485915</v>
       </c>
       <c r="W41">
-        <v>0.2172531012607448</v>
+        <v>0.2177167737292262</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3932760546915853</v>
+        <v>0.3834441533242957</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5195,22 +5195,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1636035405884118</v>
+        <v>0.1655035405884118</v>
       </c>
       <c r="C42">
-        <v>29.47011675277628</v>
+        <v>17.00460055808622</v>
       </c>
       <c r="D42">
-        <v>313.7746543573552</v>
+        <v>308.7942516027796</v>
       </c>
       <c r="E42">
-        <v>282.7931935931317</v>
+        <v>290.2783070332462</v>
       </c>
       <c r="F42">
-        <v>299.4045376045789</v>
+        <v>306.8896510446934</v>
       </c>
       <c r="G42">
         <v>15.1</v>
@@ -5231,37 +5231,37 @@
         <v>27.071</v>
       </c>
       <c r="M42">
-        <v>70.59958996715972</v>
+        <v>72.3645797163387</v>
       </c>
       <c r="N42">
-        <v>-43.52858996715972</v>
+        <v>-45.2935797163387</v>
       </c>
       <c r="O42">
-        <v>-8.705717993431945</v>
+        <v>-9.058715943267741</v>
       </c>
       <c r="P42">
-        <v>-34.82287197372777</v>
+        <v>-36.23486377307096</v>
       </c>
       <c r="Q42">
-        <v>-29.08287197372777</v>
+        <v>-30.49486377307095</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1275280518278688</v>
+        <v>0.1289132730452903</v>
       </c>
       <c r="T42">
-        <v>1.680414765845967</v>
+        <v>1.708896372046746</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07668883066485915</v>
+        <v>0.0748183713803504</v>
       </c>
       <c r="W42">
-        <v>0.2177167737292262</v>
+        <v>0.2181578280285134</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3834441533242957</v>
+        <v>0.374091856901752</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5277,22 +5277,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1655035405884118</v>
+        <v>0.1674035405884118</v>
       </c>
       <c r="C43">
-        <v>17.00460055808622</v>
+        <v>4.6947174179586</v>
       </c>
       <c r="D43">
-        <v>308.7942516027796</v>
+        <v>303.9694819027665</v>
       </c>
       <c r="E43">
-        <v>290.2783070332462</v>
+        <v>297.7634204733607</v>
       </c>
       <c r="F43">
-        <v>306.8896510446934</v>
+        <v>314.3747644848079</v>
       </c>
       <c r="G43">
         <v>15.1</v>
@@ -5313,37 +5313,37 @@
         <v>27.071</v>
       </c>
       <c r="M43">
-        <v>72.3645797163387</v>
+        <v>74.1295694655177</v>
       </c>
       <c r="N43">
-        <v>-45.2935797163387</v>
+        <v>-47.05856946551771</v>
       </c>
       <c r="O43">
-        <v>-9.058715943267741</v>
+        <v>-9.411713893103542</v>
       </c>
       <c r="P43">
-        <v>-36.23486377307096</v>
+        <v>-37.64685557241417</v>
       </c>
       <c r="Q43">
-        <v>-30.49486377307095</v>
+        <v>-31.90685557241417</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1289132730452903</v>
+        <v>0.1303462605115884</v>
       </c>
       <c r="T43">
-        <v>1.708896372046746</v>
+        <v>1.738360102599276</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.0748183713803504</v>
+        <v>0.07303698158558013</v>
       </c>
       <c r="W43">
-        <v>0.2181578280285134</v>
+        <v>0.2185778797421202</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.374091856901752</v>
+        <v>0.3651849079279006</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5359,22 +5359,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1674035405884118</v>
+        <v>0.1693035405884118</v>
       </c>
       <c r="C44">
-        <v>4.694717417958771</v>
+        <v>-7.466715525739744</v>
       </c>
       <c r="D44">
-        <v>303.9694819027666</v>
+        <v>299.2931623991826</v>
       </c>
       <c r="E44">
-        <v>297.7634204733606</v>
+        <v>305.2485339134751</v>
       </c>
       <c r="F44">
-        <v>314.3747644848078</v>
+        <v>321.8598779249223</v>
       </c>
       <c r="G44">
         <v>15.1</v>
@@ -5395,37 +5395,37 @@
         <v>27.071</v>
       </c>
       <c r="M44">
-        <v>74.12956946551769</v>
+        <v>75.89455921469668</v>
       </c>
       <c r="N44">
-        <v>-47.05856946551769</v>
+        <v>-48.82355921469669</v>
       </c>
       <c r="O44">
-        <v>-9.411713893103538</v>
+        <v>-9.764711842939338</v>
       </c>
       <c r="P44">
-        <v>-37.64685557241415</v>
+        <v>-39.05884737175735</v>
       </c>
       <c r="Q44">
-        <v>-31.90685557241415</v>
+        <v>-33.31884737175735</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1303462605115884</v>
+        <v>0.1318295282398619</v>
       </c>
       <c r="T44">
-        <v>1.738360102599276</v>
+        <v>1.768857648258912</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07303698158558014</v>
+        <v>0.07133844713010154</v>
       </c>
       <c r="W44">
-        <v>0.2185778797421202</v>
+        <v>0.2189783941667221</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3651849079279007</v>
+        <v>0.3566922356505077</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5441,22 +5441,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1693035405884118</v>
+        <v>0.1712035405884118</v>
       </c>
       <c r="C45">
-        <v>-7.466715525739744</v>
+        <v>-19.48644581869769</v>
       </c>
       <c r="D45">
-        <v>299.2931623991826</v>
+        <v>294.7585455463391</v>
       </c>
       <c r="E45">
-        <v>305.2485339134751</v>
+        <v>312.7336473535896</v>
       </c>
       <c r="F45">
-        <v>321.8598779249223</v>
+        <v>329.3449913650368</v>
       </c>
       <c r="G45">
         <v>15.1</v>
@@ -5477,37 +5477,37 @@
         <v>27.071</v>
       </c>
       <c r="M45">
-        <v>75.89455921469668</v>
+        <v>77.65954896387568</v>
       </c>
       <c r="N45">
-        <v>-48.82355921469669</v>
+        <v>-50.58854896387568</v>
       </c>
       <c r="O45">
-        <v>-9.764711842939338</v>
+        <v>-10.11770979277514</v>
       </c>
       <c r="P45">
-        <v>-39.05884737175735</v>
+        <v>-40.47083917110054</v>
       </c>
       <c r="Q45">
-        <v>-33.31884737175735</v>
+        <v>-34.73083917110054</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1318295282398619</v>
+        <v>0.1333657698155737</v>
       </c>
       <c r="T45">
-        <v>1.768857648258912</v>
+        <v>1.800444391977822</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.07133844713010154</v>
+        <v>0.06971711878623559</v>
       </c>
       <c r="W45">
-        <v>0.2189783941667221</v>
+        <v>0.2193607033902057</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3566922356505077</v>
+        <v>0.3485855939311779</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5523,22 +5523,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1712035405884118</v>
+        <v>0.1731035405884118</v>
       </c>
       <c r="C46">
-        <v>-19.48644581869769</v>
+        <v>-31.370818179259</v>
       </c>
       <c r="D46">
-        <v>294.7585455463391</v>
+        <v>290.3592866258923</v>
       </c>
       <c r="E46">
-        <v>312.7336473535896</v>
+        <v>320.2187607937041</v>
       </c>
       <c r="F46">
-        <v>329.3449913650368</v>
+        <v>336.8301048051513</v>
       </c>
       <c r="G46">
         <v>15.1</v>
@@ -5559,37 +5559,37 @@
         <v>27.071</v>
       </c>
       <c r="M46">
-        <v>77.65954896387568</v>
+        <v>79.42453871305467</v>
       </c>
       <c r="N46">
-        <v>-50.58854896387568</v>
+        <v>-52.35353871305468</v>
       </c>
       <c r="O46">
-        <v>-10.11770979277514</v>
+        <v>-10.47070774261094</v>
       </c>
       <c r="P46">
-        <v>-40.47083917110054</v>
+        <v>-41.88283097044374</v>
       </c>
       <c r="Q46">
-        <v>-34.73083917110054</v>
+        <v>-36.14283097044374</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1333657698155737</v>
+        <v>0.1349578747213114</v>
       </c>
       <c r="T46">
-        <v>1.800444391977822</v>
+        <v>1.833179744559236</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06971711878623559</v>
+        <v>0.0681678494798748</v>
       </c>
       <c r="W46">
-        <v>0.2193607033902057</v>
+        <v>0.2197260210926456</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3485855939311779</v>
+        <v>0.340839247399374</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5605,22 +5605,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1731035405884118</v>
+        <v>0.1750035405884118</v>
       </c>
       <c r="C47">
-        <v>-31.370818179259</v>
+        <v>-43.12580411726901</v>
       </c>
       <c r="D47">
-        <v>290.3592866258923</v>
+        <v>286.0894141279967</v>
       </c>
       <c r="E47">
-        <v>320.2187607937041</v>
+        <v>327.7038742338185</v>
       </c>
       <c r="F47">
-        <v>336.8301048051513</v>
+        <v>344.3152182452657</v>
       </c>
       <c r="G47">
         <v>15.1</v>
@@ -5641,37 +5641,37 @@
         <v>27.071</v>
       </c>
       <c r="M47">
-        <v>79.42453871305467</v>
+        <v>81.18952846223367</v>
       </c>
       <c r="N47">
-        <v>-52.35353871305468</v>
+        <v>-54.11852846223367</v>
       </c>
       <c r="O47">
-        <v>-10.47070774261094</v>
+        <v>-10.82370569244673</v>
       </c>
       <c r="P47">
-        <v>-41.88283097044374</v>
+        <v>-43.29482276978693</v>
       </c>
       <c r="Q47">
-        <v>-36.14283097044374</v>
+        <v>-37.55482276978693</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1349578747213114</v>
+        <v>0.1366089464754098</v>
       </c>
       <c r="T47">
-        <v>1.833179744559236</v>
+        <v>1.86712751760663</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0681678494798748</v>
+        <v>0.06668593970857317</v>
       </c>
       <c r="W47">
-        <v>0.2197260210926456</v>
+        <v>0.2200754554167185</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.340839247399374</v>
+        <v>0.3334296985428659</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5687,22 +5687,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1750035405884118</v>
+        <v>0.1769035405884118</v>
       </c>
       <c r="C48">
-        <v>-43.12580411726901</v>
+        <v>-54.7570289774381</v>
       </c>
       <c r="D48">
-        <v>286.0894141279967</v>
+        <v>281.9433027079421</v>
       </c>
       <c r="E48">
-        <v>327.7038742338185</v>
+        <v>335.188987673933</v>
       </c>
       <c r="F48">
-        <v>344.3152182452657</v>
+        <v>351.8003316853802</v>
       </c>
       <c r="G48">
         <v>15.1</v>
@@ -5723,37 +5723,37 @@
         <v>27.071</v>
       </c>
       <c r="M48">
-        <v>81.18952846223367</v>
+        <v>82.95451821141266</v>
       </c>
       <c r="N48">
-        <v>-54.11852846223367</v>
+        <v>-55.88351821141266</v>
       </c>
       <c r="O48">
-        <v>-10.82370569244673</v>
+        <v>-11.17670364228253</v>
       </c>
       <c r="P48">
-        <v>-43.29482276978693</v>
+        <v>-44.70681456913013</v>
       </c>
       <c r="Q48">
-        <v>-37.55482276978693</v>
+        <v>-38.96681456913013</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1366089464754098</v>
+        <v>0.1383223228240024</v>
       </c>
       <c r="T48">
-        <v>1.86712751760663</v>
+        <v>1.902356338693547</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06668593970857317</v>
+        <v>0.0652670899275397</v>
       </c>
       <c r="W48">
-        <v>0.2200754554167185</v>
+        <v>0.2204100201950862</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3334296985428659</v>
+        <v>0.3263354496376984</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5769,22 +5769,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1769035405884118</v>
+        <v>0.1788035405884118</v>
       </c>
       <c r="C49">
-        <v>-54.7570289774381</v>
+        <v>-66.2697966647641</v>
       </c>
       <c r="D49">
-        <v>281.9433027079421</v>
+        <v>277.9156484607306</v>
       </c>
       <c r="E49">
-        <v>335.188987673933</v>
+        <v>342.6741011140475</v>
       </c>
       <c r="F49">
-        <v>351.8003316853802</v>
+        <v>359.2854451254947</v>
       </c>
       <c r="G49">
         <v>15.1</v>
@@ -5805,37 +5805,37 @@
         <v>27.071</v>
       </c>
       <c r="M49">
-        <v>82.95451821141266</v>
+        <v>84.71950796059166</v>
       </c>
       <c r="N49">
-        <v>-55.88351821141266</v>
+        <v>-57.64850796059166</v>
       </c>
       <c r="O49">
-        <v>-11.17670364228253</v>
+        <v>-11.52970159211833</v>
       </c>
       <c r="P49">
-        <v>-44.70681456913013</v>
+        <v>-46.11880636847333</v>
       </c>
       <c r="Q49">
-        <v>-38.96681456913013</v>
+        <v>-40.37880636847333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1383223228240024</v>
+        <v>0.1401015982629255</v>
       </c>
       <c r="T49">
-        <v>1.902356338693547</v>
+        <v>1.938940114437654</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0652670899275397</v>
+        <v>0.06390735888738262</v>
       </c>
       <c r="W49">
-        <v>0.2204100201950862</v>
+        <v>0.2207306447743552</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3263354496376984</v>
+        <v>0.3195367944369131</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1788035405884117</v>
+        <v>0.1807035405884118</v>
       </c>
       <c r="C50">
-        <v>-66.26979666476404</v>
+        <v>-77.66911228053846</v>
       </c>
       <c r="D50">
-        <v>277.9156484607306</v>
+        <v>274.0014462850706</v>
       </c>
       <c r="E50">
-        <v>342.6741011140475</v>
+        <v>350.1592145541619</v>
       </c>
       <c r="F50">
-        <v>359.2854451254947</v>
+        <v>366.7705585656091</v>
       </c>
       <c r="G50">
         <v>15.1</v>
@@ -5887,37 +5887,37 @@
         <v>27.071</v>
       </c>
       <c r="M50">
-        <v>84.71950796059164</v>
+        <v>86.48449770977064</v>
       </c>
       <c r="N50">
-        <v>-57.64850796059164</v>
+        <v>-59.41349770977064</v>
       </c>
       <c r="O50">
-        <v>-11.52970159211833</v>
+        <v>-11.88269954195413</v>
       </c>
       <c r="P50">
-        <v>-46.11880636847332</v>
+        <v>-47.53079816781651</v>
       </c>
       <c r="Q50">
-        <v>-40.37880636847331</v>
+        <v>-41.79079816781651</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1401015982629255</v>
+        <v>0.1419506492092574</v>
       </c>
       <c r="T50">
-        <v>1.938940114437654</v>
+        <v>1.976958548054078</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06390735888738262</v>
+        <v>0.06260312707335441</v>
       </c>
       <c r="W50">
-        <v>0.2207306447743552</v>
+        <v>0.221038182636103</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3195367944369132</v>
+        <v>0.313015635366772</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5933,22 +5933,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1807035405884118</v>
+        <v>0.1826035405884118</v>
       </c>
       <c r="C51">
-        <v>-77.66911228053846</v>
+        <v>-88.95970287206615</v>
       </c>
       <c r="D51">
-        <v>274.0014462850706</v>
+        <v>270.1959691336575</v>
       </c>
       <c r="E51">
-        <v>350.1592145541619</v>
+        <v>357.6443279942764</v>
       </c>
       <c r="F51">
-        <v>366.7705585656091</v>
+        <v>374.2556720057236</v>
       </c>
       <c r="G51">
         <v>15.1</v>
@@ -5969,37 +5969,37 @@
         <v>27.071</v>
       </c>
       <c r="M51">
-        <v>86.48449770977064</v>
+        <v>88.24948745894963</v>
       </c>
       <c r="N51">
-        <v>-59.41349770977064</v>
+        <v>-61.17848745894963</v>
       </c>
       <c r="O51">
-        <v>-11.88269954195413</v>
+        <v>-12.23569749178993</v>
       </c>
       <c r="P51">
-        <v>-47.53079816781651</v>
+        <v>-48.9427899671597</v>
       </c>
       <c r="Q51">
-        <v>-41.79079816781651</v>
+        <v>-43.2027899671597</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1419506492092574</v>
+        <v>0.1438736621934426</v>
       </c>
       <c r="T51">
-        <v>1.976958548054078</v>
+        <v>2.01649771901516</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06260312707335441</v>
+        <v>0.06135106453188732</v>
       </c>
       <c r="W51">
-        <v>0.221038182636103</v>
+        <v>0.221333418983381</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.313015635366772</v>
+        <v>0.3067553226594366</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6015,22 +6015,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1826035405884118</v>
+        <v>0.1845035405884118</v>
       </c>
       <c r="C52">
-        <v>-88.95970287206615</v>
+        <v>-100.1460364769732</v>
       </c>
       <c r="D52">
-        <v>270.1959691336575</v>
+        <v>266.4947489688649</v>
       </c>
       <c r="E52">
-        <v>357.6443279942764</v>
+        <v>365.1294414343909</v>
       </c>
       <c r="F52">
-        <v>374.2556720057236</v>
+        <v>381.7407854458381</v>
       </c>
       <c r="G52">
         <v>15.1</v>
@@ -6051,37 +6051,37 @@
         <v>27.071</v>
       </c>
       <c r="M52">
-        <v>88.24948745894963</v>
+        <v>90.01447720812864</v>
       </c>
       <c r="N52">
-        <v>-61.17848745894963</v>
+        <v>-62.94347720812864</v>
       </c>
       <c r="O52">
-        <v>-12.23569749178993</v>
+        <v>-12.58869544162573</v>
       </c>
       <c r="P52">
-        <v>-48.9427899671597</v>
+        <v>-50.35478176650291</v>
       </c>
       <c r="Q52">
-        <v>-43.2027899671597</v>
+        <v>-44.61478176650291</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1438736621934426</v>
+        <v>0.1458751655035128</v>
       </c>
       <c r="T52">
-        <v>2.01649771901516</v>
+        <v>2.057650733688939</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06135106453188732</v>
+        <v>0.06014810248224246</v>
       </c>
       <c r="W52">
-        <v>0.221333418983381</v>
+        <v>0.2216170774346872</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3067553226594366</v>
+        <v>0.3007405124112124</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6097,22 +6097,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1845035405884118</v>
+        <v>0.1864035405884117</v>
       </c>
       <c r="C53">
-        <v>-100.1460364769732</v>
+        <v>-111.2323396234197</v>
       </c>
       <c r="D53">
-        <v>266.4947489688649</v>
+        <v>262.8935592625328</v>
       </c>
       <c r="E53">
-        <v>365.1294414343909</v>
+        <v>372.6145548745054</v>
       </c>
       <c r="F53">
-        <v>381.7407854458381</v>
+        <v>389.2258988859526</v>
       </c>
       <c r="G53">
         <v>15.1</v>
@@ -6133,37 +6133,37 @@
         <v>27.071</v>
       </c>
       <c r="M53">
-        <v>90.01447720812864</v>
+        <v>91.77946695730762</v>
       </c>
       <c r="N53">
-        <v>-62.94347720812864</v>
+        <v>-64.70846695730762</v>
       </c>
       <c r="O53">
-        <v>-12.58869544162573</v>
+        <v>-12.94169339146153</v>
       </c>
       <c r="P53">
-        <v>-50.35478176650291</v>
+        <v>-51.76677356584609</v>
       </c>
       <c r="Q53">
-        <v>-44.61478176650291</v>
+        <v>-46.02677356584609</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1458751655035128</v>
+        <v>0.147960064784836</v>
       </c>
       <c r="T53">
-        <v>2.057650733688939</v>
+        <v>2.100518457307458</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06014810248224246</v>
+        <v>0.05899140820373781</v>
       </c>
       <c r="W53">
-        <v>0.2216170774346872</v>
+        <v>0.2218898259455586</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3007405124112124</v>
+        <v>0.294957041018689</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6179,22 +6179,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1864035405884117</v>
+        <v>0.1883035405884118</v>
       </c>
       <c r="C54">
-        <v>-111.2323396234197</v>
+        <v>-122.2226134303317</v>
       </c>
       <c r="D54">
-        <v>262.8935592625328</v>
+        <v>259.3883988957353</v>
       </c>
       <c r="E54">
-        <v>372.6145548745054</v>
+        <v>380.0996683146199</v>
       </c>
       <c r="F54">
-        <v>389.2258988859526</v>
+        <v>396.7110123260671</v>
       </c>
       <c r="G54">
         <v>15.1</v>
@@ -6215,37 +6215,37 @@
         <v>27.071</v>
       </c>
       <c r="M54">
-        <v>91.77946695730762</v>
+        <v>93.54445670648663</v>
       </c>
       <c r="N54">
-        <v>-64.70846695730762</v>
+        <v>-66.47345670648663</v>
       </c>
       <c r="O54">
-        <v>-12.94169339146153</v>
+        <v>-13.29469134129733</v>
       </c>
       <c r="P54">
-        <v>-51.76677356584609</v>
+        <v>-53.17876536518931</v>
       </c>
       <c r="Q54">
-        <v>-46.02677356584609</v>
+        <v>-47.4387653651893</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.147960064784836</v>
+        <v>0.1501336831845133</v>
       </c>
       <c r="T54">
-        <v>2.100518457307458</v>
+        <v>2.14521033937783</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05899140820373781</v>
+        <v>0.05787836276593143</v>
       </c>
       <c r="W54">
-        <v>0.2218898259455586</v>
+        <v>0.2221522820597934</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.294957041018689</v>
+        <v>0.2893918138296571</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6261,22 +6261,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1883035405884118</v>
+        <v>0.1902035405884118</v>
       </c>
       <c r="C55">
-        <v>-122.2226134303317</v>
+        <v>-133.1206484365912</v>
       </c>
       <c r="D55">
-        <v>259.3883988957353</v>
+        <v>255.9754773295903</v>
       </c>
       <c r="E55">
-        <v>380.0996683146199</v>
+        <v>387.5847817547343</v>
       </c>
       <c r="F55">
-        <v>396.7110123260671</v>
+        <v>404.1961257661815</v>
       </c>
       <c r="G55">
         <v>15.1</v>
@@ -6297,37 +6297,37 @@
         <v>27.071</v>
       </c>
       <c r="M55">
-        <v>93.54445670648663</v>
+        <v>95.30944645566561</v>
       </c>
       <c r="N55">
-        <v>-66.47345670648663</v>
+        <v>-68.23844645566561</v>
       </c>
       <c r="O55">
-        <v>-13.29469134129733</v>
+        <v>-13.64768929113312</v>
       </c>
       <c r="P55">
-        <v>-53.17876536518931</v>
+        <v>-54.59075716453249</v>
       </c>
       <c r="Q55">
-        <v>-47.4387653651893</v>
+        <v>-48.85075716453249</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1501336831845133</v>
+        <v>0.1524018067320028</v>
       </c>
       <c r="T55">
-        <v>2.14521033937783</v>
+        <v>2.191845346755609</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05787836276593143</v>
+        <v>0.05680654123322901</v>
       </c>
       <c r="W55">
-        <v>0.2221522820597934</v>
+        <v>0.2224050175772046</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2893918138296571</v>
+        <v>0.284032706166145</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6343,22 +6343,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1902035405884118</v>
+        <v>0.1921035405884118</v>
       </c>
       <c r="C56">
-        <v>-133.1206484365912</v>
+        <v>-143.9300382747354</v>
       </c>
       <c r="D56">
-        <v>255.9754773295903</v>
+        <v>252.6512009315606</v>
       </c>
       <c r="E56">
-        <v>387.5847817547343</v>
+        <v>395.0698951948488</v>
       </c>
       <c r="F56">
-        <v>404.1961257661815</v>
+        <v>411.681239206296</v>
       </c>
       <c r="G56">
         <v>15.1</v>
@@ -6379,37 +6379,37 @@
         <v>27.071</v>
       </c>
       <c r="M56">
-        <v>95.30944645566561</v>
+        <v>97.0744362048446</v>
       </c>
       <c r="N56">
-        <v>-68.23844645566561</v>
+        <v>-70.0034362048446</v>
       </c>
       <c r="O56">
-        <v>-13.64768929113312</v>
+        <v>-14.00068724096892</v>
       </c>
       <c r="P56">
-        <v>-54.59075716453249</v>
+        <v>-56.00274896387568</v>
       </c>
       <c r="Q56">
-        <v>-48.85075716453249</v>
+        <v>-50.26274896387568</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1524018067320028</v>
+        <v>0.1547707357704917</v>
       </c>
       <c r="T56">
-        <v>2.191845346755609</v>
+        <v>2.240553021127956</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05680654123322901</v>
+        <v>0.05577369502898847</v>
       </c>
       <c r="W56">
-        <v>0.2224050175772046</v>
+        <v>0.2226485627121645</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.284032706166145</v>
+        <v>0.2788684751449424</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6425,22 +6425,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1921035405884118</v>
+        <v>0.1940035405884118</v>
       </c>
       <c r="C57">
-        <v>-143.9300382747354</v>
+        <v>-154.6541922928555</v>
       </c>
       <c r="D57">
-        <v>252.6512009315606</v>
+        <v>249.412160353555</v>
       </c>
       <c r="E57">
-        <v>395.0698951948488</v>
+        <v>402.5550086349633</v>
       </c>
       <c r="F57">
-        <v>411.681239206296</v>
+        <v>419.1663526464105</v>
       </c>
       <c r="G57">
         <v>15.1</v>
@@ -6461,37 +6461,37 @@
         <v>27.071</v>
       </c>
       <c r="M57">
-        <v>97.0744362048446</v>
+        <v>98.8394259540236</v>
       </c>
       <c r="N57">
-        <v>-70.0034362048446</v>
+        <v>-71.7684259540236</v>
       </c>
       <c r="O57">
-        <v>-14.00068724096892</v>
+        <v>-14.35368519080472</v>
       </c>
       <c r="P57">
-        <v>-56.00274896387568</v>
+        <v>-57.41474076321888</v>
       </c>
       <c r="Q57">
-        <v>-50.26274896387568</v>
+        <v>-51.67474076321888</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1547707357704917</v>
+        <v>0.1572473434016393</v>
       </c>
       <c r="T57">
-        <v>2.240553021127956</v>
+        <v>2.291474680699046</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05577369502898847</v>
+        <v>0.05477773618918511</v>
       </c>
       <c r="W57">
-        <v>0.2226485627121645</v>
+        <v>0.2228834098065902</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2788684751449424</v>
+        <v>0.2738886809459256</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6507,22 +6507,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1940035405884118</v>
+        <v>0.1959035405884118</v>
       </c>
       <c r="C58">
-        <v>-154.6541922928555</v>
+        <v>-165.2963472178951</v>
       </c>
       <c r="D58">
-        <v>249.412160353555</v>
+        <v>246.2551188686299</v>
       </c>
       <c r="E58">
-        <v>402.5550086349633</v>
+        <v>410.0401220750778</v>
       </c>
       <c r="F58">
-        <v>419.1663526464105</v>
+        <v>426.651466086525</v>
       </c>
       <c r="G58">
         <v>15.1</v>
@@ -6543,37 +6543,37 @@
         <v>27.071</v>
       </c>
       <c r="M58">
-        <v>98.8394259540236</v>
+        <v>100.6044157032026</v>
       </c>
       <c r="N58">
-        <v>-71.7684259540236</v>
+        <v>-73.53341570320259</v>
       </c>
       <c r="O58">
-        <v>-14.35368519080472</v>
+        <v>-14.70668314064052</v>
       </c>
       <c r="P58">
-        <v>-57.41474076321888</v>
+        <v>-58.82673256256207</v>
       </c>
       <c r="Q58">
-        <v>-51.67474076321888</v>
+        <v>-53.08673256256207</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1572473434016393</v>
+        <v>0.1598391420853983</v>
       </c>
       <c r="T58">
-        <v>2.291474680699046</v>
+        <v>2.344764789552512</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05477773618918511</v>
+        <v>0.05381672327358537</v>
       </c>
       <c r="W58">
-        <v>0.2228834098065902</v>
+        <v>0.2231100166520886</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2738886809459256</v>
+        <v>0.2690836163679268</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6589,22 +6589,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1959035405884118</v>
+        <v>0.1978035405884118</v>
       </c>
       <c r="C59">
-        <v>-165.2963472178951</v>
+        <v>-175.8595779442201</v>
       </c>
       <c r="D59">
-        <v>246.2551188686299</v>
+        <v>243.1770015824194</v>
       </c>
       <c r="E59">
-        <v>410.0401220750778</v>
+        <v>417.5252355151923</v>
       </c>
       <c r="F59">
-        <v>426.651466086525</v>
+        <v>434.1365795266395</v>
       </c>
       <c r="G59">
         <v>15.1</v>
@@ -6625,37 +6625,37 @@
         <v>27.071</v>
       </c>
       <c r="M59">
-        <v>100.6044157032026</v>
+        <v>102.3694054523816</v>
       </c>
       <c r="N59">
-        <v>-73.53341570320259</v>
+        <v>-75.2984054523816</v>
       </c>
       <c r="O59">
-        <v>-14.70668314064052</v>
+        <v>-15.05968109047632</v>
       </c>
       <c r="P59">
-        <v>-58.82673256256207</v>
+        <v>-60.23872436190528</v>
       </c>
       <c r="Q59">
-        <v>-53.08673256256207</v>
+        <v>-54.49872436190528</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1598391420853983</v>
+        <v>0.1625543597540983</v>
       </c>
       <c r="T59">
-        <v>2.344764789552512</v>
+        <v>2.400592522637096</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05381672327358537</v>
+        <v>0.05288884873438561</v>
       </c>
       <c r="W59">
-        <v>0.2231100166520886</v>
+        <v>0.2233288094684319</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2690836163679268</v>
+        <v>0.264444243671928</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6671,22 +6671,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1978035405884118</v>
+        <v>0.1997035405884118</v>
       </c>
       <c r="C60">
-        <v>-175.85957794422</v>
+        <v>-186.3468075230543</v>
       </c>
       <c r="D60">
-        <v>243.1770015824194</v>
+        <v>240.1748854436996</v>
       </c>
       <c r="E60">
-        <v>417.5252355151922</v>
+        <v>425.0103489553067</v>
       </c>
       <c r="F60">
-        <v>434.1365795266394</v>
+        <v>441.6216929667539</v>
       </c>
       <c r="G60">
         <v>15.1</v>
@@ -6707,37 +6707,37 @@
         <v>27.071</v>
       </c>
       <c r="M60">
-        <v>102.3694054523816</v>
+        <v>104.1343952015606</v>
       </c>
       <c r="N60">
-        <v>-75.29840545238157</v>
+        <v>-77.06339520156057</v>
       </c>
       <c r="O60">
-        <v>-15.05968109047632</v>
+        <v>-15.41267904031211</v>
       </c>
       <c r="P60">
-        <v>-60.23872436190526</v>
+        <v>-61.65071616124845</v>
       </c>
       <c r="Q60">
-        <v>-54.49872436190525</v>
+        <v>-55.91071616124845</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1625543597540983</v>
+        <v>0.1654020270651738</v>
       </c>
       <c r="T60">
-        <v>2.400592522637095</v>
+        <v>2.459143559774585</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05288884873438562</v>
+        <v>0.05199242756939604</v>
       </c>
       <c r="W60">
-        <v>0.2233288094684319</v>
+        <v>0.2235401855791364</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2644442436719281</v>
+        <v>0.2599621378469802</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6753,22 +6753,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1997035405884118</v>
+        <v>0.2016035405884118</v>
       </c>
       <c r="C61">
-        <v>-186.3468075230543</v>
+        <v>-196.7608164209974</v>
       </c>
       <c r="D61">
-        <v>240.1748854436996</v>
+        <v>237.2459899858709</v>
       </c>
       <c r="E61">
-        <v>425.0103489553067</v>
+        <v>432.4954623954211</v>
       </c>
       <c r="F61">
-        <v>441.6216929667539</v>
+        <v>449.1068064068683</v>
       </c>
       <c r="G61">
         <v>15.1</v>
@@ -6789,37 +6789,37 @@
         <v>27.071</v>
       </c>
       <c r="M61">
-        <v>104.1343952015606</v>
+        <v>105.8993849507396</v>
       </c>
       <c r="N61">
-        <v>-77.06339520156057</v>
+        <v>-78.82838495073956</v>
       </c>
       <c r="O61">
-        <v>-15.41267904031211</v>
+        <v>-15.76567699014791</v>
       </c>
       <c r="P61">
-        <v>-61.65071616124845</v>
+        <v>-63.06270796059165</v>
       </c>
       <c r="Q61">
-        <v>-55.91071616124845</v>
+        <v>-57.32270796059165</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1654020270651738</v>
+        <v>0.1683920777418032</v>
       </c>
       <c r="T61">
-        <v>2.459143559774585</v>
+        <v>2.52062214876895</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05199242756939604</v>
+        <v>0.0511258871099061</v>
       </c>
       <c r="W61">
-        <v>0.2235401855791364</v>
+        <v>0.2237445158194842</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2599621378469802</v>
+        <v>0.2556294355495305</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6835,22 +6835,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2016035405884118</v>
+        <v>0.2035035405884117</v>
       </c>
       <c r="C62">
-        <v>-196.7608164209974</v>
+        <v>-207.1042511092671</v>
       </c>
       <c r="D62">
-        <v>237.2459899858709</v>
+        <v>234.3876687377157</v>
       </c>
       <c r="E62">
-        <v>432.4954623954211</v>
+        <v>439.9805758355356</v>
       </c>
       <c r="F62">
-        <v>449.1068064068683</v>
+        <v>456.5919198469828</v>
       </c>
       <c r="G62">
         <v>15.1</v>
@@ -6871,37 +6871,37 @@
         <v>27.071</v>
       </c>
       <c r="M62">
-        <v>105.8993849507396</v>
+        <v>107.6643746999186</v>
       </c>
       <c r="N62">
-        <v>-78.82838495073956</v>
+        <v>-80.59337469991856</v>
       </c>
       <c r="O62">
-        <v>-15.76567699014791</v>
+        <v>-16.11867493998371</v>
       </c>
       <c r="P62">
-        <v>-63.06270796059165</v>
+        <v>-64.47469975993485</v>
       </c>
       <c r="Q62">
-        <v>-57.32270796059165</v>
+        <v>-58.73469975993485</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1683920777418032</v>
+        <v>0.1715354643505674</v>
       </c>
       <c r="T62">
-        <v>2.52062214876895</v>
+        <v>2.585253485916872</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0511258871099061</v>
+        <v>0.05028775781302239</v>
       </c>
       <c r="W62">
-        <v>0.2237445158194842</v>
+        <v>0.2239421467076893</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2556294355495305</v>
+        <v>0.251438789065112</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2035035405884117</v>
+        <v>0.2054035405884118</v>
       </c>
       <c r="C63">
-        <v>-207.1042511092671</v>
+        <v>-217.3796320394375</v>
       </c>
       <c r="D63">
-        <v>234.3876687377157</v>
+        <v>231.5974012476598</v>
       </c>
       <c r="E63">
-        <v>439.9805758355356</v>
+        <v>447.46568927565</v>
       </c>
       <c r="F63">
-        <v>456.5919198469828</v>
+        <v>464.0770332870973</v>
       </c>
       <c r="G63">
         <v>15.1</v>
@@ -6953,37 +6953,37 @@
         <v>27.071</v>
       </c>
       <c r="M63">
-        <v>107.6643746999186</v>
+        <v>109.4293644490975</v>
       </c>
       <c r="N63">
-        <v>-80.59337469991856</v>
+        <v>-82.35836444909754</v>
       </c>
       <c r="O63">
-        <v>-16.11867493998371</v>
+        <v>-16.47167288981951</v>
       </c>
       <c r="P63">
-        <v>-64.47469975993485</v>
+        <v>-65.88669155927803</v>
       </c>
       <c r="Q63">
-        <v>-58.73469975993485</v>
+        <v>-60.14669155927803</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1715354643505674</v>
+        <v>0.1748442923597928</v>
       </c>
       <c r="T63">
-        <v>2.585253485916872</v>
+        <v>2.653286472388368</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05028775781302239</v>
+        <v>0.04947666494507043</v>
       </c>
       <c r="W63">
-        <v>0.2239421467076893</v>
+        <v>0.2241334024059524</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.251438789065112</v>
+        <v>0.2473833247253521</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6999,22 +6999,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2054035405884118</v>
+        <v>0.2073035405884118</v>
       </c>
       <c r="C64">
-        <v>-217.3796320394375</v>
+        <v>-227.5893610561973</v>
       </c>
       <c r="D64">
-        <v>231.5974012476598</v>
+        <v>228.8727856710145</v>
       </c>
       <c r="E64">
-        <v>447.46568927565</v>
+        <v>454.9508027157646</v>
       </c>
       <c r="F64">
-        <v>464.0770332870973</v>
+        <v>471.5621467272118</v>
       </c>
       <c r="G64">
         <v>15.1</v>
@@ -7035,37 +7035,37 @@
         <v>27.071</v>
       </c>
       <c r="M64">
-        <v>109.4293644490975</v>
+        <v>111.1943541982765</v>
       </c>
       <c r="N64">
-        <v>-82.35836444909754</v>
+        <v>-84.12335419827654</v>
       </c>
       <c r="O64">
-        <v>-16.47167288981951</v>
+        <v>-16.82467083965531</v>
       </c>
       <c r="P64">
-        <v>-65.88669155927803</v>
+        <v>-67.29868335862123</v>
       </c>
       <c r="Q64">
-        <v>-60.14669155927803</v>
+        <v>-61.55868335862123</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1748442923597928</v>
+        <v>0.1783319759370845</v>
       </c>
       <c r="T64">
-        <v>2.653286472388368</v>
+        <v>2.724996917588054</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04947666494507043</v>
+        <v>0.04869132105705343</v>
       </c>
       <c r="W64">
-        <v>0.2241334024059524</v>
+        <v>0.2243185864947468</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2473833247253521</v>
+        <v>0.2434566052852671</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7081,22 +7081,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2073035405884118</v>
+        <v>0.2092035405884118</v>
       </c>
       <c r="C65">
-        <v>-227.5893610561973</v>
+        <v>-237.7357282929493</v>
       </c>
       <c r="D65">
-        <v>228.8727856710145</v>
+        <v>226.211531874377</v>
       </c>
       <c r="E65">
-        <v>454.9508027157646</v>
+        <v>462.4359161558791</v>
       </c>
       <c r="F65">
-        <v>471.5621467272118</v>
+        <v>479.0472601673263</v>
       </c>
       <c r="G65">
         <v>15.1</v>
@@ -7117,37 +7117,37 @@
         <v>27.071</v>
       </c>
       <c r="M65">
-        <v>111.1943541982765</v>
+        <v>112.9593439474555</v>
       </c>
       <c r="N65">
-        <v>-84.12335419827654</v>
+        <v>-85.88834394745554</v>
       </c>
       <c r="O65">
-        <v>-16.82467083965531</v>
+        <v>-17.17766878949111</v>
       </c>
       <c r="P65">
-        <v>-67.29868335862123</v>
+        <v>-68.71067515796443</v>
       </c>
       <c r="Q65">
-        <v>-61.55868335862123</v>
+        <v>-62.97067515796443</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1783319759370845</v>
+        <v>0.1820134197131147</v>
       </c>
       <c r="T65">
-        <v>2.724996917588054</v>
+        <v>2.800691276409945</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04869132105705343</v>
+        <v>0.04793051916553697</v>
       </c>
       <c r="W65">
-        <v>0.2243185864947468</v>
+        <v>0.2244979835807664</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2434566052852671</v>
+        <v>0.2396525958276848</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7163,22 +7163,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2092035405884118</v>
+        <v>0.2111035405884118</v>
       </c>
       <c r="C66">
-        <v>-237.7357282929493</v>
+        <v>-247.8209185918618</v>
       </c>
       <c r="D66">
-        <v>226.211531874377</v>
+        <v>223.6114550155789</v>
       </c>
       <c r="E66">
-        <v>462.4359161558791</v>
+        <v>469.9210295959935</v>
       </c>
       <c r="F66">
-        <v>479.0472601673263</v>
+        <v>486.5323736074407</v>
       </c>
       <c r="G66">
         <v>15.1</v>
@@ -7199,37 +7199,37 @@
         <v>27.071</v>
       </c>
       <c r="M66">
-        <v>112.9593439474555</v>
+        <v>114.7243336966345</v>
       </c>
       <c r="N66">
-        <v>-85.88834394745554</v>
+        <v>-87.65333369663453</v>
       </c>
       <c r="O66">
-        <v>-17.17766878949111</v>
+        <v>-17.53066673932691</v>
       </c>
       <c r="P66">
-        <v>-68.71067515796443</v>
+        <v>-70.12266695730763</v>
       </c>
       <c r="Q66">
-        <v>-62.97067515796443</v>
+        <v>-64.38266695730763</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1820134197131147</v>
+        <v>0.185905231704918</v>
       </c>
       <c r="T66">
-        <v>2.800691276409945</v>
+        <v>2.880711027164515</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04793051916553697</v>
+        <v>0.04719312656299024</v>
       </c>
       <c r="W66">
-        <v>0.2244979835807664</v>
+        <v>0.2246718607564469</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2396525958276848</v>
+        <v>0.2359656328149512</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7245,22 +7245,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2111035405884118</v>
+        <v>0.2130035405884118</v>
       </c>
       <c r="C67">
-        <v>-247.8209185918618</v>
+        <v>-257.8470174861985</v>
       </c>
       <c r="D67">
-        <v>223.6114550155789</v>
+        <v>221.0704695613567</v>
       </c>
       <c r="E67">
-        <v>469.9210295959935</v>
+        <v>477.406143036108</v>
       </c>
       <c r="F67">
-        <v>486.5323736074407</v>
+        <v>494.0174870475552</v>
       </c>
       <c r="G67">
         <v>15.1</v>
@@ -7281,37 +7281,37 @@
         <v>27.071</v>
       </c>
       <c r="M67">
-        <v>114.7243336966345</v>
+        <v>116.4893234458135</v>
       </c>
       <c r="N67">
-        <v>-87.65333369663453</v>
+        <v>-89.41832344581353</v>
       </c>
       <c r="O67">
-        <v>-17.53066673932691</v>
+        <v>-17.88366468916271</v>
       </c>
       <c r="P67">
-        <v>-70.12266695730763</v>
+        <v>-71.53465875665083</v>
       </c>
       <c r="Q67">
-        <v>-64.38266695730763</v>
+        <v>-65.79465875665083</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.185905231704918</v>
+        <v>0.1900259738138861</v>
       </c>
       <c r="T67">
-        <v>2.880711027164515</v>
+        <v>2.965437822081118</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04719312656299024</v>
+        <v>0.04647807919082372</v>
       </c>
       <c r="W67">
-        <v>0.2246718607564469</v>
+        <v>0.2248404689268038</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2359656328149512</v>
+        <v>0.2323903959541186</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7327,22 +7327,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2130035405884118</v>
+        <v>0.2149035405884118</v>
       </c>
       <c r="C68">
-        <v>-257.8470174861985</v>
+        <v>-267.8160167793532</v>
       </c>
       <c r="D68">
-        <v>221.0704695613567</v>
+        <v>218.5865837083165</v>
       </c>
       <c r="E68">
-        <v>477.406143036108</v>
+        <v>484.8912564762225</v>
       </c>
       <c r="F68">
-        <v>494.0174870475552</v>
+        <v>501.5026004876697</v>
       </c>
       <c r="G68">
         <v>15.1</v>
@@ -7363,37 +7363,37 @@
         <v>27.071</v>
       </c>
       <c r="M68">
-        <v>116.4893234458135</v>
+        <v>118.2543131949925</v>
       </c>
       <c r="N68">
-        <v>-89.41832344581353</v>
+        <v>-91.18331319499251</v>
       </c>
       <c r="O68">
-        <v>-17.88366468916271</v>
+        <v>-18.2366626389985</v>
       </c>
       <c r="P68">
-        <v>-71.53465875665083</v>
+        <v>-72.94665055599401</v>
       </c>
       <c r="Q68">
-        <v>-65.79465875665083</v>
+        <v>-67.20665055599402</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1900259738138861</v>
+        <v>0.1943964578688524</v>
       </c>
       <c r="T68">
-        <v>2.965437822081118</v>
+        <v>3.055299574265395</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04647807919082372</v>
+        <v>0.04578437651633382</v>
       </c>
       <c r="W68">
-        <v>0.2248404689268038</v>
+        <v>0.2250040440174485</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2323903959541186</v>
+        <v>0.2289218825816691</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7409,22 +7409,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2149035405884118</v>
+        <v>0.2168035405884118</v>
       </c>
       <c r="C69">
-        <v>-267.8160167793532</v>
+        <v>-277.7298197519577</v>
       </c>
       <c r="D69">
-        <v>218.5865837083165</v>
+        <v>216.1578941758265</v>
       </c>
       <c r="E69">
-        <v>484.8912564762225</v>
+        <v>492.376369916337</v>
       </c>
       <c r="F69">
-        <v>501.5026004876697</v>
+        <v>508.9877139277842</v>
       </c>
       <c r="G69">
         <v>15.1</v>
@@ -7445,37 +7445,37 @@
         <v>27.071</v>
       </c>
       <c r="M69">
-        <v>118.2543131949925</v>
+        <v>120.0193029441715</v>
       </c>
       <c r="N69">
-        <v>-91.18331319499251</v>
+        <v>-92.94830294417152</v>
       </c>
       <c r="O69">
-        <v>-18.2366626389985</v>
+        <v>-18.5896605888343</v>
       </c>
       <c r="P69">
-        <v>-72.94665055599401</v>
+        <v>-74.35864235533721</v>
       </c>
       <c r="Q69">
-        <v>-67.20665055599402</v>
+        <v>-68.61864235533722</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1943964578688524</v>
+        <v>0.199040097177254</v>
       </c>
       <c r="T69">
-        <v>3.055299574265395</v>
+        <v>3.150777685961188</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04578437651633382</v>
+        <v>0.04511107686168185</v>
       </c>
       <c r="W69">
-        <v>0.2250040440174485</v>
+        <v>0.2251628080760154</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2289218825816691</v>
+        <v>0.2255553843084093</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7491,22 +7491,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2168035405884118</v>
+        <v>0.2187035405884118</v>
       </c>
       <c r="C70">
-        <v>-277.7298197519577</v>
+        <v>-287.5902460256694</v>
       </c>
       <c r="D70">
-        <v>216.1578941758265</v>
+        <v>213.7825813422292</v>
       </c>
       <c r="E70">
-        <v>492.376369916337</v>
+        <v>499.8614833564514</v>
       </c>
       <c r="F70">
-        <v>508.9877139277842</v>
+        <v>516.4728273678986</v>
       </c>
       <c r="G70">
         <v>15.1</v>
@@ -7527,37 +7527,37 @@
         <v>27.071</v>
       </c>
       <c r="M70">
-        <v>120.0193029441715</v>
+        <v>121.7842926933505</v>
       </c>
       <c r="N70">
-        <v>-92.94830294417152</v>
+        <v>-94.7132926933505</v>
       </c>
       <c r="O70">
-        <v>-18.5896605888343</v>
+        <v>-18.9426585386701</v>
       </c>
       <c r="P70">
-        <v>-74.35864235533721</v>
+        <v>-75.77063415468039</v>
       </c>
       <c r="Q70">
-        <v>-68.61864235533722</v>
+        <v>-70.0306341546804</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.199040097177254</v>
+        <v>0.2039833261184558</v>
       </c>
       <c r="T70">
-        <v>3.150777685961188</v>
+        <v>3.252415675830904</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04511107686168185</v>
+        <v>0.04445729313904878</v>
       </c>
       <c r="W70">
-        <v>0.2251628080760154</v>
+        <v>0.2253169702778123</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2255553843084093</v>
+        <v>0.2222864656952439</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7573,22 +7573,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2187035405884118</v>
+        <v>0.2206035405884118</v>
       </c>
       <c r="C71">
-        <v>-287.5902460256694</v>
+        <v>-297.3990361097636</v>
       </c>
       <c r="D71">
-        <v>213.7825813422292</v>
+        <v>211.4589046982495</v>
       </c>
       <c r="E71">
-        <v>499.8614833564514</v>
+        <v>507.346596796566</v>
       </c>
       <c r="F71">
-        <v>516.4728273678986</v>
+        <v>523.9579408080132</v>
       </c>
       <c r="G71">
         <v>15.1</v>
@@ -7609,37 +7609,37 @@
         <v>27.071</v>
       </c>
       <c r="M71">
-        <v>121.7842926933505</v>
+        <v>123.5492824425295</v>
       </c>
       <c r="N71">
-        <v>-94.7132926933505</v>
+        <v>-96.47828244252952</v>
       </c>
       <c r="O71">
-        <v>-18.9426585386701</v>
+        <v>-19.29565648850591</v>
       </c>
       <c r="P71">
-        <v>-75.77063415468039</v>
+        <v>-77.18262595402362</v>
       </c>
       <c r="Q71">
-        <v>-70.0306341546804</v>
+        <v>-71.44262595402363</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2039833261184558</v>
+        <v>0.2092561036557376</v>
       </c>
       <c r="T71">
-        <v>3.252415675830904</v>
+        <v>3.360829531691934</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04445729313904878</v>
+        <v>0.04382218895134807</v>
       </c>
       <c r="W71">
-        <v>0.2253169702778123</v>
+        <v>0.2254667278452721</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2222864656952439</v>
+        <v>0.2191109447567404</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7655,22 +7655,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2206035405884118</v>
+        <v>0.2225035405884118</v>
       </c>
       <c r="C72">
-        <v>-297.3990361097636</v>
+        <v>-307.157855654401</v>
       </c>
       <c r="D72">
-        <v>211.4589046982495</v>
+        <v>209.1851985937266</v>
       </c>
       <c r="E72">
-        <v>507.346596796566</v>
+        <v>514.8317102366804</v>
       </c>
       <c r="F72">
-        <v>523.9579408080132</v>
+        <v>531.4430542481276</v>
       </c>
       <c r="G72">
         <v>15.1</v>
@@ -7691,37 +7691,37 @@
         <v>27.071</v>
       </c>
       <c r="M72">
-        <v>123.5492824425295</v>
+        <v>125.3142721917085</v>
       </c>
       <c r="N72">
-        <v>-96.47828244252952</v>
+        <v>-98.2432721917085</v>
       </c>
       <c r="O72">
-        <v>-19.29565648850591</v>
+        <v>-19.6486544383417</v>
       </c>
       <c r="P72">
-        <v>-77.18262595402362</v>
+        <v>-78.5946177533668</v>
       </c>
       <c r="Q72">
-        <v>-71.44262595402363</v>
+        <v>-72.85461775336681</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2092561036557376</v>
+        <v>0.2148925210231769</v>
       </c>
       <c r="T72">
-        <v>3.360829531691934</v>
+        <v>3.476720205198553</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04382218895134807</v>
+        <v>0.04320497502245586</v>
       </c>
       <c r="W72">
-        <v>0.2254667278452721</v>
+        <v>0.2256122668897049</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2191109447567404</v>
+        <v>0.2160248751122793</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7737,22 +7737,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2225035405884118</v>
+        <v>0.2244035405884118</v>
       </c>
       <c r="C73">
-        <v>-307.1578556544008</v>
+        <v>-316.8682994324171</v>
       </c>
       <c r="D73">
-        <v>209.1851985937267</v>
+        <v>206.9598682558249</v>
       </c>
       <c r="E73">
-        <v>514.8317102366802</v>
+        <v>522.3168236767947</v>
       </c>
       <c r="F73">
-        <v>531.4430542481275</v>
+        <v>538.928167688242</v>
       </c>
       <c r="G73">
         <v>15.1</v>
@@ -7773,37 +7773,37 @@
         <v>27.071</v>
       </c>
       <c r="M73">
-        <v>125.3142721917085</v>
+        <v>127.0792619408875</v>
       </c>
       <c r="N73">
-        <v>-98.24327219170847</v>
+        <v>-100.0082619408875</v>
       </c>
       <c r="O73">
-        <v>-19.64865443834169</v>
+        <v>-20.00165238817749</v>
       </c>
       <c r="P73">
-        <v>-78.59461775336678</v>
+        <v>-80.00660955270997</v>
       </c>
       <c r="Q73">
-        <v>-72.85461775336678</v>
+        <v>-74.26660955270998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2148925210231768</v>
+        <v>0.2209315396311474</v>
       </c>
       <c r="T73">
-        <v>3.476720205198552</v>
+        <v>3.600888783955643</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04320497502245586</v>
+        <v>0.04260490592492176</v>
       </c>
       <c r="W73">
-        <v>0.2256122668897049</v>
+        <v>0.2257537631829035</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2160248751122793</v>
+        <v>0.2130245296246087</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7819,22 +7819,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2244035405884118</v>
+        <v>0.2263035405884118</v>
       </c>
       <c r="C74">
-        <v>-316.8682994324171</v>
+        <v>-326.5318950696355</v>
       </c>
       <c r="D74">
-        <v>206.9598682558249</v>
+        <v>204.781386058721</v>
       </c>
       <c r="E74">
-        <v>522.3168236767947</v>
+        <v>529.8019371169092</v>
       </c>
       <c r="F74">
-        <v>538.928167688242</v>
+        <v>546.4132811283565</v>
       </c>
       <c r="G74">
         <v>15.1</v>
@@ -7855,37 +7855,37 @@
         <v>27.071</v>
       </c>
       <c r="M74">
-        <v>127.0792619408875</v>
+        <v>128.8442516900665</v>
       </c>
       <c r="N74">
-        <v>-100.0082619408875</v>
+        <v>-101.7732516900665</v>
       </c>
       <c r="O74">
-        <v>-20.00165238817749</v>
+        <v>-20.3546503380133</v>
       </c>
       <c r="P74">
-        <v>-80.00660955270997</v>
+        <v>-81.41860135205317</v>
       </c>
       <c r="Q74">
-        <v>-74.26660955270998</v>
+        <v>-75.67860135205318</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2209315396311474</v>
+        <v>0.2274178929508195</v>
       </c>
       <c r="T74">
-        <v>3.600888783955643</v>
+        <v>3.734255035213259</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04260490592492176</v>
+        <v>0.04202127707663515</v>
       </c>
       <c r="W74">
-        <v>0.2257537631829035</v>
+        <v>0.2258913828653294</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2130245296246087</v>
+        <v>0.2101063853831757</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7901,22 +7901,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2263035405884118</v>
+        <v>0.2282035405884117</v>
       </c>
       <c r="C75">
-        <v>-326.5318950696355</v>
+        <v>-336.1501065420383</v>
       </c>
       <c r="D75">
-        <v>204.781386058721</v>
+        <v>202.6482880264327</v>
       </c>
       <c r="E75">
-        <v>529.8019371169092</v>
+        <v>537.2870505570237</v>
       </c>
       <c r="F75">
-        <v>546.4132811283565</v>
+        <v>553.898394568471</v>
       </c>
       <c r="G75">
         <v>15.1</v>
@@ -7937,37 +7937,37 @@
         <v>27.071</v>
       </c>
       <c r="M75">
-        <v>128.8442516900665</v>
+        <v>130.6092414392455</v>
       </c>
       <c r="N75">
-        <v>-101.7732516900665</v>
+        <v>-103.5382414392455</v>
       </c>
       <c r="O75">
-        <v>-20.3546503380133</v>
+        <v>-20.7076482878491</v>
       </c>
       <c r="P75">
-        <v>-81.41860135205317</v>
+        <v>-82.83059315139637</v>
       </c>
       <c r="Q75">
-        <v>-75.67860135205318</v>
+        <v>-77.09059315139638</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2274178929508195</v>
+        <v>0.234403196525851</v>
       </c>
       <c r="T75">
-        <v>3.734255035213259</v>
+        <v>3.877880228875307</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04202127707663515</v>
+        <v>0.04145342198100494</v>
       </c>
       <c r="W75">
-        <v>0.2258913828653294</v>
+        <v>0.226025283096879</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2101063853831757</v>
+        <v>0.2072671099050247</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7983,22 +7983,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2282035405884117</v>
+        <v>0.2301035405884118</v>
       </c>
       <c r="C76">
-        <v>-336.1501065420383</v>
+        <v>-345.7243374566243</v>
       </c>
       <c r="D76">
-        <v>202.6482880264327</v>
+        <v>200.5591705519612</v>
       </c>
       <c r="E76">
-        <v>537.2870505570237</v>
+        <v>544.7721639971381</v>
       </c>
       <c r="F76">
-        <v>553.898394568471</v>
+        <v>561.3835080085854</v>
       </c>
       <c r="G76">
         <v>15.1</v>
@@ -8019,37 +8019,37 @@
         <v>27.071</v>
       </c>
       <c r="M76">
-        <v>130.6092414392455</v>
+        <v>132.3742311884244</v>
       </c>
       <c r="N76">
-        <v>-103.5382414392455</v>
+        <v>-105.3032311884244</v>
       </c>
       <c r="O76">
-        <v>-20.7076482878491</v>
+        <v>-21.06064623768489</v>
       </c>
       <c r="P76">
-        <v>-82.83059315139637</v>
+        <v>-84.24258495073954</v>
       </c>
       <c r="Q76">
-        <v>-77.09059315139638</v>
+        <v>-78.50258495073955</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.234403196525851</v>
+        <v>0.2419473243868851</v>
       </c>
       <c r="T76">
-        <v>3.877880228875307</v>
+        <v>4.03299543803032</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04145342198100494</v>
+        <v>0.04090070968792489</v>
       </c>
       <c r="W76">
-        <v>0.226025283096879</v>
+        <v>0.2261556126555873</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2072671099050247</v>
+        <v>0.2045035484396244</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8065,22 +8065,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2301035405884118</v>
+        <v>0.2320035405884118</v>
       </c>
       <c r="C77">
-        <v>-345.7243374566243</v>
+        <v>-355.2559341313999</v>
       </c>
       <c r="D77">
-        <v>200.5591705519612</v>
+        <v>198.5126873173001</v>
       </c>
       <c r="E77">
-        <v>544.7721639971381</v>
+        <v>552.2572774372527</v>
       </c>
       <c r="F77">
-        <v>561.3835080085854</v>
+        <v>568.8686214487</v>
       </c>
       <c r="G77">
         <v>15.1</v>
@@ -8101,37 +8101,37 @@
         <v>27.071</v>
       </c>
       <c r="M77">
-        <v>132.3742311884244</v>
+        <v>134.1392209376035</v>
       </c>
       <c r="N77">
-        <v>-105.3032311884244</v>
+        <v>-107.0682209376035</v>
       </c>
       <c r="O77">
-        <v>-21.06064623768489</v>
+        <v>-21.41364418752069</v>
       </c>
       <c r="P77">
-        <v>-84.24258495073954</v>
+        <v>-85.65457675008277</v>
       </c>
       <c r="Q77">
-        <v>-78.50258495073955</v>
+        <v>-79.91457675008277</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2419473243868851</v>
+        <v>0.2501201295696719</v>
       </c>
       <c r="T77">
-        <v>4.03299543803032</v>
+        <v>4.201036914614916</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04090070968792489</v>
+        <v>0.04036254245518903</v>
       </c>
       <c r="W77">
-        <v>0.2261556126555873</v>
+        <v>0.2262825124890664</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2045035484396244</v>
+        <v>0.2018127122759451</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8147,22 +8147,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2320035405884118</v>
+        <v>0.2339035405884118</v>
       </c>
       <c r="C78">
-        <v>-355.2559341313999</v>
+        <v>-364.7461884887084</v>
       </c>
       <c r="D78">
-        <v>198.5126873173001</v>
+        <v>196.507546400106</v>
       </c>
       <c r="E78">
-        <v>552.2572774372527</v>
+        <v>559.7423908773671</v>
       </c>
       <c r="F78">
-        <v>568.8686214487</v>
+        <v>576.3537348888144</v>
       </c>
       <c r="G78">
         <v>15.1</v>
@@ -8183,37 +8183,37 @@
         <v>27.071</v>
       </c>
       <c r="M78">
-        <v>134.1392209376035</v>
+        <v>135.9042106867824</v>
       </c>
       <c r="N78">
-        <v>-107.0682209376035</v>
+        <v>-108.8332106867825</v>
       </c>
       <c r="O78">
-        <v>-21.41364418752069</v>
+        <v>-21.76664213735649</v>
       </c>
       <c r="P78">
-        <v>-85.65457675008277</v>
+        <v>-87.06656854942597</v>
       </c>
       <c r="Q78">
-        <v>-79.91457675008277</v>
+        <v>-81.32656854942597</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2501201295696719</v>
+        <v>0.2590036134640055</v>
       </c>
       <c r="T78">
-        <v>4.201036914614916</v>
+        <v>4.383690693511218</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04036254245518903</v>
+        <v>0.03983835359213462</v>
       </c>
       <c r="W78">
-        <v>0.2262825124890664</v>
+        <v>0.2264061162229747</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2018127122759451</v>
+        <v>0.1991917679606731</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8229,22 +8229,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2339035405884118</v>
+        <v>0.2358035405884118</v>
       </c>
       <c r="C79">
-        <v>-364.7461884887084</v>
+        <v>-374.1963407749619</v>
       </c>
       <c r="D79">
-        <v>196.507546400106</v>
+        <v>194.542507553967</v>
       </c>
       <c r="E79">
-        <v>559.7423908773671</v>
+        <v>567.2275043174816</v>
       </c>
       <c r="F79">
-        <v>576.3537348888144</v>
+        <v>583.8388483289289</v>
       </c>
       <c r="G79">
         <v>15.1</v>
@@ -8265,37 +8265,37 @@
         <v>27.071</v>
       </c>
       <c r="M79">
-        <v>135.9042106867824</v>
+        <v>137.6692004359614</v>
       </c>
       <c r="N79">
-        <v>-108.8332106867825</v>
+        <v>-110.5982004359614</v>
       </c>
       <c r="O79">
-        <v>-21.76664213735649</v>
+        <v>-22.11964008719229</v>
       </c>
       <c r="P79">
-        <v>-87.06656854942597</v>
+        <v>-88.47856034876915</v>
       </c>
       <c r="Q79">
-        <v>-81.32656854942597</v>
+        <v>-82.73856034876916</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2590036134640055</v>
+        <v>0.2686946868032786</v>
       </c>
       <c r="T79">
-        <v>4.383690693511218</v>
+        <v>4.582949361398092</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03983835359213462</v>
+        <v>0.03932760546915853</v>
       </c>
       <c r="W79">
-        <v>0.2264061162229747</v>
+        <v>0.2265265506303724</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1991917679606731</v>
+        <v>0.1966380273457927</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8311,22 +8311,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2358035405884118</v>
+        <v>0.2377035405884118</v>
       </c>
       <c r="C80">
-        <v>-374.1963407749619</v>
+        <v>-383.6075821188095</v>
       </c>
       <c r="D80">
-        <v>194.542507553967</v>
+        <v>192.6163796502338</v>
       </c>
       <c r="E80">
-        <v>567.2275043174816</v>
+        <v>574.712617757596</v>
       </c>
       <c r="F80">
-        <v>583.8388483289289</v>
+        <v>591.3239617690433</v>
       </c>
       <c r="G80">
         <v>15.1</v>
@@ -8347,37 +8347,37 @@
         <v>27.071</v>
       </c>
       <c r="M80">
-        <v>137.6692004359614</v>
+        <v>139.4341901851404</v>
       </c>
       <c r="N80">
-        <v>-110.5982004359614</v>
+        <v>-112.3631901851404</v>
       </c>
       <c r="O80">
-        <v>-22.11964008719229</v>
+        <v>-22.47263803702808</v>
       </c>
       <c r="P80">
-        <v>-88.47856034876915</v>
+        <v>-89.89055214811233</v>
       </c>
       <c r="Q80">
-        <v>-82.73856034876916</v>
+        <v>-84.15055214811234</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2686946868032786</v>
+        <v>0.2793087195081966</v>
       </c>
       <c r="T80">
-        <v>4.582949361398092</v>
+        <v>4.801185045274192</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03932760546915853</v>
+        <v>0.0388297876784097</v>
       </c>
       <c r="W80">
-        <v>0.2265265506303724</v>
+        <v>0.226643936065431</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1966380273457927</v>
+        <v>0.1941489383920485</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8393,22 +8393,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2377035405884118</v>
+        <v>0.2396035405884118</v>
       </c>
       <c r="C81">
-        <v>-383.6075821188095</v>
+        <v>-392.9810569388262</v>
       </c>
       <c r="D81">
-        <v>192.6163796502338</v>
+        <v>190.7280182703317</v>
       </c>
       <c r="E81">
-        <v>574.712617757596</v>
+        <v>582.1977311977106</v>
       </c>
       <c r="F81">
-        <v>591.3239617690433</v>
+        <v>598.8090752091579</v>
       </c>
       <c r="G81">
         <v>15.1</v>
@@ -8429,37 +8429,37 @@
         <v>27.071</v>
       </c>
       <c r="M81">
-        <v>139.4341901851404</v>
+        <v>141.1991799343194</v>
       </c>
       <c r="N81">
-        <v>-112.3631901851404</v>
+        <v>-114.1281799343194</v>
       </c>
       <c r="O81">
-        <v>-22.47263803702808</v>
+        <v>-22.82563598686389</v>
       </c>
       <c r="P81">
-        <v>-89.89055214811233</v>
+        <v>-91.30254394745555</v>
       </c>
       <c r="Q81">
-        <v>-84.15055214811234</v>
+        <v>-85.56254394745555</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2793087195081966</v>
+        <v>0.2909841554836065</v>
       </c>
       <c r="T81">
-        <v>4.801185045274192</v>
+        <v>5.041244297537902</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0388297876784097</v>
+        <v>0.03834441533242958</v>
       </c>
       <c r="W81">
-        <v>0.226643936065431</v>
+        <v>0.2267583868646131</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1941489383920485</v>
+        <v>0.1917220766621478</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8475,22 +8475,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2396035405884118</v>
+        <v>0.2415035405884118</v>
       </c>
       <c r="C82">
-        <v>-392.9810569388262</v>
+        <v>-402.3178652109507</v>
       </c>
       <c r="D82">
-        <v>190.7280182703317</v>
+        <v>188.8763234383216</v>
       </c>
       <c r="E82">
-        <v>582.1977311977106</v>
+        <v>589.682844637825</v>
       </c>
       <c r="F82">
-        <v>598.8090752091579</v>
+        <v>606.2941886492723</v>
       </c>
       <c r="G82">
         <v>15.1</v>
@@ -8511,37 +8511,37 @@
         <v>27.071</v>
       </c>
       <c r="M82">
-        <v>141.1991799343194</v>
+        <v>142.9641696834984</v>
       </c>
       <c r="N82">
-        <v>-114.1281799343194</v>
+        <v>-115.8931696834984</v>
       </c>
       <c r="O82">
-        <v>-22.82563598686389</v>
+        <v>-23.17863393669969</v>
       </c>
       <c r="P82">
-        <v>-91.30254394745555</v>
+        <v>-92.71453574679875</v>
       </c>
       <c r="Q82">
-        <v>-85.56254394745555</v>
+        <v>-86.97453574679875</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2909841554836065</v>
+        <v>0.3038885847195857</v>
       </c>
       <c r="T82">
-        <v>5.041244297537902</v>
+        <v>5.306572944776739</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03834441533242958</v>
+        <v>0.03787102748881933</v>
       </c>
       <c r="W82">
-        <v>0.2267583868646131</v>
+        <v>0.2268700117181364</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1917220766621478</v>
+        <v>0.1893551374440966</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8557,22 +8557,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2415035405884118</v>
+        <v>0.2434035405884118</v>
       </c>
       <c r="C83">
-        <v>-402.3178652109507</v>
+        <v>-411.6190646051134</v>
       </c>
       <c r="D83">
-        <v>188.8763234383216</v>
+        <v>187.0602374842734</v>
       </c>
       <c r="E83">
-        <v>589.682844637825</v>
+        <v>597.1679580779395</v>
       </c>
       <c r="F83">
-        <v>606.2941886492723</v>
+        <v>613.7793020893868</v>
       </c>
       <c r="G83">
         <v>15.1</v>
@@ -8593,37 +8593,37 @@
         <v>27.071</v>
       </c>
       <c r="M83">
-        <v>142.9641696834984</v>
+        <v>144.7291594326774</v>
       </c>
       <c r="N83">
-        <v>-115.8931696834984</v>
+        <v>-117.6581594326774</v>
       </c>
       <c r="O83">
-        <v>-23.17863393669969</v>
+        <v>-23.53163188653548</v>
       </c>
       <c r="P83">
-        <v>-92.71453574679875</v>
+        <v>-94.12652754614192</v>
       </c>
       <c r="Q83">
-        <v>-86.97453574679875</v>
+        <v>-88.38652754614192</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3038885847195857</v>
+        <v>0.3182268394262294</v>
       </c>
       <c r="T83">
-        <v>5.306572944776739</v>
+        <v>5.601382552819891</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03787102748881933</v>
+        <v>0.0374091856901752</v>
       </c>
       <c r="W83">
-        <v>0.2268700117181364</v>
+        <v>0.2269789140142567</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1893551374440966</v>
+        <v>0.187045928450876</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8639,22 +8639,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2434035405884118</v>
+        <v>0.2453035405884118</v>
       </c>
       <c r="C84">
-        <v>-411.6190646051134</v>
+        <v>-420.8856724997718</v>
       </c>
       <c r="D84">
-        <v>187.0602374842734</v>
+        <v>185.2787430297296</v>
       </c>
       <c r="E84">
-        <v>597.1679580779395</v>
+        <v>604.653071518054</v>
       </c>
       <c r="F84">
-        <v>613.7793020893868</v>
+        <v>621.2644155295013</v>
       </c>
       <c r="G84">
         <v>15.1</v>
@@ -8675,37 +8675,37 @@
         <v>27.071</v>
       </c>
       <c r="M84">
-        <v>144.7291594326774</v>
+        <v>146.4941491818564</v>
       </c>
       <c r="N84">
-        <v>-117.6581594326774</v>
+        <v>-119.4231491818564</v>
       </c>
       <c r="O84">
-        <v>-23.53163188653548</v>
+        <v>-23.88462983637129</v>
       </c>
       <c r="P84">
-        <v>-94.12652754614192</v>
+        <v>-95.53851934548513</v>
       </c>
       <c r="Q84">
-        <v>-88.38652754614192</v>
+        <v>-89.79851934548513</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3182268394262294</v>
+        <v>0.3342519476277723</v>
       </c>
       <c r="T84">
-        <v>5.601382552819891</v>
+        <v>5.930875644162239</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0374091856901752</v>
+        <v>0.03695847260957067</v>
       </c>
       <c r="W84">
-        <v>0.2269789140142567</v>
+        <v>0.2270851921586632</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.187045928450876</v>
+        <v>0.1847923630478533</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8721,22 +8721,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2453035405884118</v>
+        <v>0.2472035405884118</v>
       </c>
       <c r="C85">
-        <v>-420.8856724997718</v>
+        <v>-430.1186678824183</v>
       </c>
       <c r="D85">
-        <v>185.2787430297296</v>
+        <v>183.5308610871975</v>
       </c>
       <c r="E85">
-        <v>604.653071518054</v>
+        <v>612.1381849581685</v>
       </c>
       <c r="F85">
-        <v>621.2644155295013</v>
+        <v>628.7495289696158</v>
       </c>
       <c r="G85">
         <v>15.1</v>
@@ -8757,37 +8757,37 @@
         <v>27.071</v>
       </c>
       <c r="M85">
-        <v>146.4941491818564</v>
+        <v>148.2591389310354</v>
       </c>
       <c r="N85">
-        <v>-119.4231491818564</v>
+        <v>-121.1881389310354</v>
       </c>
       <c r="O85">
-        <v>-23.88462983637129</v>
+        <v>-24.23762778620709</v>
       </c>
       <c r="P85">
-        <v>-95.53851934548513</v>
+        <v>-96.95051114482833</v>
       </c>
       <c r="Q85">
-        <v>-89.79851934548513</v>
+        <v>-91.21051114482833</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3342519476277723</v>
+        <v>0.3522801943545081</v>
       </c>
       <c r="T85">
-        <v>5.930875644162239</v>
+        <v>6.301555371922379</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03695847260957067</v>
+        <v>0.03651849079279006</v>
       </c>
       <c r="W85">
-        <v>0.2270851921586632</v>
+        <v>0.2271889398710601</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1847923630478533</v>
+        <v>0.1825924539639503</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8803,22 +8803,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2472035405884118</v>
+        <v>0.2491035405884118</v>
       </c>
       <c r="C86">
-        <v>-430.118667882418</v>
+        <v>-439.3189931435191</v>
       </c>
       <c r="D86">
-        <v>183.5308610871976</v>
+        <v>181.815649266211</v>
       </c>
       <c r="E86">
-        <v>612.1381849581684</v>
+        <v>619.6232983982828</v>
       </c>
       <c r="F86">
-        <v>628.7495289696157</v>
+        <v>636.2346424097301</v>
       </c>
       <c r="G86">
         <v>15.1</v>
@@ -8839,37 +8839,37 @@
         <v>27.071</v>
       </c>
       <c r="M86">
-        <v>148.2591389310354</v>
+        <v>150.0241286802144</v>
       </c>
       <c r="N86">
-        <v>-121.1881389310354</v>
+        <v>-122.9531286802144</v>
       </c>
       <c r="O86">
-        <v>-24.23762778620708</v>
+        <v>-24.59062573604288</v>
       </c>
       <c r="P86">
-        <v>-96.95051114482831</v>
+        <v>-98.3625029441715</v>
       </c>
       <c r="Q86">
-        <v>-91.21051114482832</v>
+        <v>-92.6225029441715</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.352280194354508</v>
+        <v>0.3727122073114751</v>
       </c>
       <c r="T86">
-        <v>6.301555371922375</v>
+        <v>6.721659063383867</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03651849079279007</v>
+        <v>0.03608886148934548</v>
       </c>
       <c r="W86">
-        <v>0.2271889398710601</v>
+        <v>0.2272902464608123</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1825924539639504</v>
+        <v>0.1804443074467275</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8885,22 +8885,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2491035405884118</v>
+        <v>0.2510035405884118</v>
       </c>
       <c r="C87">
-        <v>-439.3189931435191</v>
+        <v>-448.4875557707931</v>
       </c>
       <c r="D87">
-        <v>181.815649266211</v>
+        <v>180.1322000790516</v>
       </c>
       <c r="E87">
-        <v>619.6232983982828</v>
+        <v>627.1084118383974</v>
       </c>
       <c r="F87">
-        <v>636.2346424097301</v>
+        <v>643.7197558498447</v>
       </c>
       <c r="G87">
         <v>15.1</v>
@@ -8921,37 +8921,37 @@
         <v>27.071</v>
       </c>
       <c r="M87">
-        <v>150.0241286802144</v>
+        <v>151.7891184293934</v>
       </c>
       <c r="N87">
-        <v>-122.9531286802144</v>
+        <v>-124.7181184293934</v>
       </c>
       <c r="O87">
-        <v>-24.59062573604288</v>
+        <v>-24.94362368587868</v>
       </c>
       <c r="P87">
-        <v>-98.3625029441715</v>
+        <v>-99.77449474351469</v>
       </c>
       <c r="Q87">
-        <v>-92.6225029441715</v>
+        <v>-94.0344947435147</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3727122073114751</v>
+        <v>0.3960630792622948</v>
       </c>
       <c r="T87">
-        <v>6.721659063383867</v>
+        <v>7.201777567911286</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03608886148934548</v>
+        <v>0.03566922356505077</v>
       </c>
       <c r="W87">
-        <v>0.2272902464608123</v>
+        <v>0.227389197083361</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1804443074467275</v>
+        <v>0.1783461178252538</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8967,22 +8967,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2510035405884118</v>
+        <v>0.2529035405884117</v>
       </c>
       <c r="C88">
-        <v>-448.4875557707931</v>
+        <v>-457.6252299502257</v>
       </c>
       <c r="D88">
-        <v>180.1322000790516</v>
+        <v>178.4796393397334</v>
       </c>
       <c r="E88">
-        <v>627.1084118383974</v>
+        <v>634.5935252785118</v>
       </c>
       <c r="F88">
-        <v>643.7197558498447</v>
+        <v>651.2048692899591</v>
       </c>
       <c r="G88">
         <v>15.1</v>
@@ -9003,37 +9003,37 @@
         <v>27.071</v>
       </c>
       <c r="M88">
-        <v>151.7891184293934</v>
+        <v>153.5541081785724</v>
       </c>
       <c r="N88">
-        <v>-124.7181184293934</v>
+        <v>-126.4831081785724</v>
       </c>
       <c r="O88">
-        <v>-24.94362368587868</v>
+        <v>-25.29662163571447</v>
       </c>
       <c r="P88">
-        <v>-99.77449474351469</v>
+        <v>-101.1864865428579</v>
       </c>
       <c r="Q88">
-        <v>-94.0344947435147</v>
+        <v>-95.4464865428579</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3960630792622948</v>
+        <v>0.4230063930517021</v>
       </c>
       <c r="T88">
-        <v>7.201777567911286</v>
+        <v>7.755760457750616</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03566922356505077</v>
+        <v>0.03525923248959042</v>
       </c>
       <c r="W88">
-        <v>0.227389197083361</v>
+        <v>0.2274858729789546</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1783461178252538</v>
+        <v>0.1762961624479521</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9049,22 +9049,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2529035405884117</v>
+        <v>0.2548035405884118</v>
       </c>
       <c r="C89">
-        <v>-457.6252299502257</v>
+        <v>-466.7328580797602</v>
       </c>
       <c r="D89">
-        <v>178.4796393397334</v>
+        <v>176.8571246503134</v>
       </c>
       <c r="E89">
-        <v>634.5935252785118</v>
+        <v>642.0786387186263</v>
       </c>
       <c r="F89">
-        <v>651.2048692899591</v>
+        <v>658.6899827300736</v>
       </c>
       <c r="G89">
         <v>15.1</v>
@@ -9085,37 +9085,37 @@
         <v>27.071</v>
       </c>
       <c r="M89">
-        <v>153.5541081785724</v>
+        <v>155.3190979277514</v>
       </c>
       <c r="N89">
-        <v>-126.4831081785724</v>
+        <v>-128.2480979277514</v>
       </c>
       <c r="O89">
-        <v>-25.29662163571447</v>
+        <v>-25.64961958555027</v>
       </c>
       <c r="P89">
-        <v>-101.1864865428579</v>
+        <v>-102.5984783422011</v>
       </c>
       <c r="Q89">
-        <v>-95.4464865428579</v>
+        <v>-96.8584783422011</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4230063930517021</v>
+        <v>0.4544402591393439</v>
       </c>
       <c r="T89">
-        <v>7.755760457750616</v>
+        <v>8.402073829229833</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03525923248959042</v>
+        <v>0.03485855939311779</v>
       </c>
       <c r="W89">
-        <v>0.2274858729789546</v>
+        <v>0.2275803516951029</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1762961624479521</v>
+        <v>0.174292796965589</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9131,22 +9131,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2548035405884118</v>
+        <v>0.2567035405884118</v>
       </c>
       <c r="C90">
-        <v>-466.7328580797602</v>
+        <v>-475.8112522011668</v>
       </c>
       <c r="D90">
-        <v>176.8571246503134</v>
+        <v>175.2638439690214</v>
       </c>
       <c r="E90">
-        <v>642.0786387186263</v>
+        <v>649.5637521587408</v>
       </c>
       <c r="F90">
-        <v>658.6899827300736</v>
+        <v>666.1750961701881</v>
       </c>
       <c r="G90">
         <v>15.1</v>
@@ -9167,37 +9167,37 @@
         <v>27.071</v>
       </c>
       <c r="M90">
-        <v>155.3190979277514</v>
+        <v>157.0840876769304</v>
       </c>
       <c r="N90">
-        <v>-128.2480979277514</v>
+        <v>-130.0130876769304</v>
       </c>
       <c r="O90">
-        <v>-25.64961958555027</v>
+        <v>-26.00261753538607</v>
       </c>
       <c r="P90">
-        <v>-102.5984783422011</v>
+        <v>-104.0104701415443</v>
       </c>
       <c r="Q90">
-        <v>-96.8584783422011</v>
+        <v>-98.27047014154429</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4544402591393439</v>
+        <v>0.4915893736065571</v>
       </c>
       <c r="T90">
-        <v>8.402073829229833</v>
+        <v>9.165898722796184</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03485855939311779</v>
+        <v>0.03446689018645355</v>
       </c>
       <c r="W90">
-        <v>0.2275803516951029</v>
+        <v>0.2276727072940343</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.174292796965589</v>
+        <v>0.1723344509322677</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9213,22 +9213,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2567035405884118</v>
+        <v>0.2586035405884118</v>
       </c>
       <c r="C91">
-        <v>-475.8112522011668</v>
+        <v>-484.861195355206</v>
       </c>
       <c r="D91">
-        <v>175.2638439690214</v>
+        <v>173.6990142550966</v>
       </c>
       <c r="E91">
-        <v>649.5637521587408</v>
+        <v>657.0488655988553</v>
       </c>
       <c r="F91">
-        <v>666.1750961701881</v>
+        <v>673.6602096103026</v>
       </c>
       <c r="G91">
         <v>15.1</v>
@@ -9249,37 +9249,37 @@
         <v>27.071</v>
       </c>
       <c r="M91">
-        <v>157.0840876769304</v>
+        <v>158.8490774261093</v>
       </c>
       <c r="N91">
-        <v>-130.0130876769304</v>
+        <v>-131.7780774261093</v>
       </c>
       <c r="O91">
-        <v>-26.00261753538607</v>
+        <v>-26.35561548522187</v>
       </c>
       <c r="P91">
-        <v>-104.0104701415443</v>
+        <v>-105.4224619408875</v>
       </c>
       <c r="Q91">
-        <v>-98.27047014154429</v>
+        <v>-99.68246194088748</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4915893736065571</v>
+        <v>0.5361683109672128</v>
       </c>
       <c r="T91">
-        <v>9.165898722796184</v>
+        <v>10.0824885950758</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03446689018645355</v>
+        <v>0.0340839247399374</v>
       </c>
       <c r="W91">
-        <v>0.2276727072940343</v>
+        <v>0.2277630105463228</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1723344509322677</v>
+        <v>0.170419623699687</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9295,22 +9295,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2586035405884118</v>
+        <v>0.2605035405884118</v>
       </c>
       <c r="C92">
-        <v>-484.861195355206</v>
+        <v>-493.8834428648388</v>
       </c>
       <c r="D92">
-        <v>173.6990142550966</v>
+        <v>172.1618801855782</v>
       </c>
       <c r="E92">
-        <v>657.0488655988553</v>
+        <v>664.5339790389697</v>
       </c>
       <c r="F92">
-        <v>673.6602096103026</v>
+        <v>681.145323050417</v>
       </c>
       <c r="G92">
         <v>15.1</v>
@@ -9331,37 +9331,37 @@
         <v>27.071</v>
       </c>
       <c r="M92">
-        <v>158.8490774261093</v>
+        <v>160.6140671752883</v>
       </c>
       <c r="N92">
-        <v>-131.7780774261093</v>
+        <v>-133.5430671752883</v>
       </c>
       <c r="O92">
-        <v>-26.35561548522187</v>
+        <v>-26.70861343505767</v>
       </c>
       <c r="P92">
-        <v>-105.4224619408875</v>
+        <v>-106.8344537402307</v>
       </c>
       <c r="Q92">
-        <v>-99.68246194088748</v>
+        <v>-101.0944537402307</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5361683109672128</v>
+        <v>0.5906536788524588</v>
       </c>
       <c r="T92">
-        <v>10.0824885950758</v>
+        <v>11.20276510563978</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0340839247399374</v>
+        <v>0.0337093761164216</v>
       </c>
       <c r="W92">
-        <v>0.2277630105463228</v>
+        <v>0.2278513291117478</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.170419623699687</v>
+        <v>0.168546880582108</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9377,22 +9377,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2605035405884118</v>
+        <v>0.2624035405884118</v>
       </c>
       <c r="C93">
-        <v>-493.8834428648388</v>
+        <v>-502.8787235508995</v>
       </c>
       <c r="D93">
-        <v>172.1618801855782</v>
+        <v>170.651712939632</v>
       </c>
       <c r="E93">
-        <v>664.5339790389697</v>
+        <v>672.0190924790842</v>
       </c>
       <c r="F93">
-        <v>681.145323050417</v>
+        <v>688.6304364905315</v>
       </c>
       <c r="G93">
         <v>15.1</v>
@@ -9413,37 +9413,37 @@
         <v>27.071</v>
       </c>
       <c r="M93">
-        <v>160.6140671752883</v>
+        <v>162.3790569244673</v>
       </c>
       <c r="N93">
-        <v>-133.5430671752883</v>
+        <v>-135.3080569244673</v>
       </c>
       <c r="O93">
-        <v>-26.70861343505767</v>
+        <v>-27.06161138489347</v>
       </c>
       <c r="P93">
-        <v>-106.8344537402307</v>
+        <v>-108.2464455395739</v>
       </c>
       <c r="Q93">
-        <v>-101.0944537402307</v>
+        <v>-102.5064455395739</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5906536788524588</v>
+        <v>0.6587603887090162</v>
       </c>
       <c r="T93">
-        <v>11.20276510563978</v>
+        <v>12.60311074384476</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0337093761164216</v>
+        <v>0.03334296985428659</v>
       </c>
       <c r="W93">
-        <v>0.2278513291117478</v>
+        <v>0.2279377277083592</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.168546880582108</v>
+        <v>0.1667148492714329</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9459,22 +9459,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2624035405884118</v>
+        <v>0.2643035405884118</v>
       </c>
       <c r="C94">
-        <v>-502.8787235508995</v>
+        <v>-511.847740884343</v>
       </c>
       <c r="D94">
-        <v>170.651712939632</v>
+        <v>169.167809046303</v>
       </c>
       <c r="E94">
-        <v>672.0190924790842</v>
+        <v>679.5042059191987</v>
       </c>
       <c r="F94">
-        <v>688.6304364905315</v>
+        <v>696.115549930646</v>
       </c>
       <c r="G94">
         <v>15.1</v>
@@ -9495,37 +9495,37 @@
         <v>27.071</v>
       </c>
       <c r="M94">
-        <v>162.3790569244673</v>
+        <v>164.1440466736463</v>
       </c>
       <c r="N94">
-        <v>-135.3080569244673</v>
+        <v>-137.0730466736463</v>
       </c>
       <c r="O94">
-        <v>-27.06161138489347</v>
+        <v>-27.41460933472927</v>
       </c>
       <c r="P94">
-        <v>-108.2464455395739</v>
+        <v>-109.6584373389171</v>
       </c>
       <c r="Q94">
-        <v>-102.5064455395739</v>
+        <v>-103.9184373389171</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6587603887090162</v>
+        <v>0.7463261585245901</v>
       </c>
       <c r="T94">
-        <v>12.60311074384476</v>
+        <v>14.40355513582258</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03334296985428659</v>
+        <v>0.03298444329671361</v>
       </c>
       <c r="W94">
-        <v>0.2279377277083592</v>
+        <v>0.228022268270635</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1667148492714329</v>
+        <v>0.1649222164835681</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9541,22 +9541,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2643035405884118</v>
+        <v>0.2662035405884118</v>
       </c>
       <c r="C95">
-        <v>-511.847740884343</v>
+        <v>-520.7911740788945</v>
       </c>
       <c r="D95">
-        <v>169.167809046303</v>
+        <v>167.7094892918659</v>
       </c>
       <c r="E95">
-        <v>679.5042059191987</v>
+        <v>686.9893193593132</v>
       </c>
       <c r="F95">
-        <v>696.115549930646</v>
+        <v>703.6006633707605</v>
       </c>
       <c r="G95">
         <v>15.1</v>
@@ -9577,37 +9577,37 @@
         <v>27.071</v>
       </c>
       <c r="M95">
-        <v>164.1440466736463</v>
+        <v>165.9090364228253</v>
       </c>
       <c r="N95">
-        <v>-137.0730466736463</v>
+        <v>-138.8380364228253</v>
       </c>
       <c r="O95">
-        <v>-27.41460933472927</v>
+        <v>-27.76760728456507</v>
       </c>
       <c r="P95">
-        <v>-109.6584373389171</v>
+        <v>-111.0704291382603</v>
       </c>
       <c r="Q95">
-        <v>-103.9184373389171</v>
+        <v>-105.3304291382603</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7463261585245901</v>
+        <v>0.8630805182786885</v>
       </c>
       <c r="T95">
-        <v>14.40355513582258</v>
+        <v>16.80414765845968</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03298444329671361</v>
+        <v>0.03263354496376985</v>
       </c>
       <c r="W95">
-        <v>0.228022268270635</v>
+        <v>0.2281050100975431</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1649222164835681</v>
+        <v>0.1631677248188492</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9623,22 +9623,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2662035405884118</v>
+        <v>0.2681035405884118</v>
       </c>
       <c r="C96">
-        <v>-520.7911740788945</v>
+        <v>-529.7096791276678</v>
       </c>
       <c r="D96">
-        <v>167.7094892918659</v>
+        <v>166.2760976832071</v>
       </c>
       <c r="E96">
-        <v>686.9893193593132</v>
+        <v>694.4744327994276</v>
       </c>
       <c r="F96">
-        <v>703.6006633707605</v>
+        <v>711.0857768108749</v>
       </c>
       <c r="G96">
         <v>15.1</v>
@@ -9659,37 +9659,37 @@
         <v>27.071</v>
       </c>
       <c r="M96">
-        <v>165.9090364228253</v>
+        <v>167.6740261720043</v>
       </c>
       <c r="N96">
-        <v>-138.8380364228253</v>
+        <v>-140.6030261720043</v>
       </c>
       <c r="O96">
-        <v>-27.76760728456507</v>
+        <v>-28.12060523440087</v>
       </c>
       <c r="P96">
-        <v>-111.0704291382603</v>
+        <v>-112.4824209376035</v>
       </c>
       <c r="Q96">
-        <v>-105.3304291382603</v>
+        <v>-106.7424209376035</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8630805182786885</v>
+        <v>1.026536621934427</v>
       </c>
       <c r="T96">
-        <v>16.80414765845968</v>
+        <v>20.16497719015163</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03263354496376985</v>
+        <v>0.03229003396415122</v>
       </c>
       <c r="W96">
-        <v>0.2281050100975431</v>
+        <v>0.2281860099912532</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1631677248188492</v>
+        <v>0.1614501698207561</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9705,22 +9705,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2681035405884118</v>
+        <v>0.2700035405884118</v>
       </c>
       <c r="C97">
-        <v>-529.7096791276678</v>
+        <v>-538.6038897870723</v>
       </c>
       <c r="D97">
-        <v>166.2760976832071</v>
+        <v>164.8670004639172</v>
       </c>
       <c r="E97">
-        <v>694.4744327994276</v>
+        <v>701.9595462395422</v>
       </c>
       <c r="F97">
-        <v>711.0857768108749</v>
+        <v>718.5708902509895</v>
       </c>
       <c r="G97">
         <v>15.1</v>
@@ -9741,37 +9741,37 @@
         <v>27.071</v>
       </c>
       <c r="M97">
-        <v>167.6740261720043</v>
+        <v>169.4390159211833</v>
       </c>
       <c r="N97">
-        <v>-140.6030261720043</v>
+        <v>-142.3680159211833</v>
       </c>
       <c r="O97">
-        <v>-28.12060523440087</v>
+        <v>-28.47360318423667</v>
       </c>
       <c r="P97">
-        <v>-112.4824209376035</v>
+        <v>-113.8944127369466</v>
       </c>
       <c r="Q97">
-        <v>-106.7424209376035</v>
+        <v>-108.1544127369467</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.026536621934427</v>
+        <v>1.271720777418034</v>
       </c>
       <c r="T97">
-        <v>20.16497719015163</v>
+        <v>25.20622148768955</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03229003396415122</v>
+        <v>0.03195367944369131</v>
       </c>
       <c r="W97">
-        <v>0.2281860099912532</v>
+        <v>0.2282653223871776</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1614501698207561</v>
+        <v>0.1597683972184566</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9787,22 +9787,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2700035405884118</v>
+        <v>0.2719035405884118</v>
       </c>
       <c r="C98">
-        <v>-538.6038897870721</v>
+        <v>-547.4744185111147</v>
       </c>
       <c r="D98">
-        <v>164.8670004639172</v>
+        <v>163.4815851799892</v>
       </c>
       <c r="E98">
-        <v>701.9595462395421</v>
+        <v>709.4446596796565</v>
       </c>
       <c r="F98">
-        <v>718.5708902509894</v>
+        <v>726.0560036911038</v>
       </c>
       <c r="G98">
         <v>15.1</v>
@@ -9823,37 +9823,37 @@
         <v>27.071</v>
       </c>
       <c r="M98">
-        <v>169.4390159211833</v>
+        <v>171.2040056703623</v>
       </c>
       <c r="N98">
-        <v>-142.3680159211833</v>
+        <v>-144.1330056703623</v>
       </c>
       <c r="O98">
-        <v>-28.47360318423666</v>
+        <v>-28.82660113407246</v>
       </c>
       <c r="P98">
-        <v>-113.8944127369466</v>
+        <v>-115.3064045362898</v>
       </c>
       <c r="Q98">
-        <v>-108.1544127369466</v>
+        <v>-109.5664045362898</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.271720777418031</v>
+        <v>1.680361036557374</v>
       </c>
       <c r="T98">
-        <v>25.20622148768948</v>
+        <v>33.6082953169193</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03195367944369131</v>
+        <v>0.03162426006798316</v>
       </c>
       <c r="W98">
-        <v>0.2282653223871776</v>
+        <v>0.2283429994759696</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1597683972184566</v>
+        <v>0.1581213003399158</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9869,22 +9869,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2719035405884118</v>
+        <v>0.2738035405884117</v>
       </c>
       <c r="C99">
-        <v>-547.4744185111147</v>
+        <v>-556.3218573389856</v>
       </c>
       <c r="D99">
-        <v>163.4815851799892</v>
+        <v>162.1192597922326</v>
       </c>
       <c r="E99">
-        <v>709.4446596796565</v>
+        <v>716.929773119771</v>
       </c>
       <c r="F99">
-        <v>726.0560036911038</v>
+        <v>733.5411171312182</v>
       </c>
       <c r="G99">
         <v>15.1</v>
@@ -9905,37 +9905,37 @@
         <v>27.071</v>
       </c>
       <c r="M99">
-        <v>171.2040056703623</v>
+        <v>172.9689954195413</v>
       </c>
       <c r="N99">
-        <v>-144.1330056703623</v>
+        <v>-145.8979954195413</v>
       </c>
       <c r="O99">
-        <v>-28.82660113407246</v>
+        <v>-29.17959908390826</v>
       </c>
       <c r="P99">
-        <v>-115.3064045362898</v>
+        <v>-116.718396335633</v>
       </c>
       <c r="Q99">
-        <v>-109.5664045362898</v>
+        <v>-110.978396335633</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.680361036557374</v>
+        <v>2.497641554836061</v>
       </c>
       <c r="T99">
-        <v>33.6082953169193</v>
+        <v>50.41244297537896</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03162426006798316</v>
+        <v>0.03130156353667721</v>
       </c>
       <c r="W99">
-        <v>0.2283429994759696</v>
+        <v>0.2284190913180515</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1581213003399158</v>
+        <v>0.1565078176833861</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9951,22 +9951,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2738035405884117</v>
+        <v>0.2757035405884118</v>
       </c>
       <c r="C100">
-        <v>-556.3218573389856</v>
+        <v>-565.1467787386335</v>
       </c>
       <c r="D100">
-        <v>162.1192597922326</v>
+        <v>160.7794518326993</v>
       </c>
       <c r="E100">
-        <v>716.929773119771</v>
+        <v>724.4148865598855</v>
       </c>
       <c r="F100">
-        <v>733.5411171312182</v>
+        <v>741.0262305713328</v>
       </c>
       <c r="G100">
         <v>15.1</v>
@@ -9987,37 +9987,37 @@
         <v>27.071</v>
       </c>
       <c r="M100">
-        <v>172.9689954195413</v>
+        <v>174.7339851687203</v>
       </c>
       <c r="N100">
-        <v>-145.8979954195413</v>
+        <v>-147.6629851687203</v>
       </c>
       <c r="O100">
-        <v>-29.17959908390826</v>
+        <v>-29.53259703374406</v>
       </c>
       <c r="P100">
-        <v>-116.718396335633</v>
+        <v>-118.1303881349762</v>
       </c>
       <c r="Q100">
-        <v>-110.978396335633</v>
+        <v>-112.3903881349762</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.497641554836061</v>
+        <v>4.949483109672124</v>
       </c>
       <c r="T100">
-        <v>50.41244297537896</v>
+        <v>100.8248859507579</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03130156353667721</v>
+        <v>0.03098538612721581</v>
       </c>
       <c r="W100">
-        <v>0.2284190913180515</v>
+        <v>0.2284936459512025</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10025,91 +10025,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1565078176833861</v>
+        <v>0.1549269306360791</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2757035405884118</v>
-      </c>
-      <c r="C101">
-        <v>-565.1467787386335</v>
-      </c>
-      <c r="D101">
-        <v>160.7794518326993</v>
-      </c>
-      <c r="E101">
-        <v>724.4148865598855</v>
-      </c>
-      <c r="F101">
-        <v>741.0262305713328</v>
-      </c>
-      <c r="G101">
-        <v>15.1</v>
-      </c>
-      <c r="H101">
-        <v>731.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>32.811</v>
-      </c>
-      <c r="K101">
-        <v>5.74</v>
-      </c>
-      <c r="L101">
-        <v>27.071</v>
-      </c>
-      <c r="M101">
-        <v>174.7339851687203</v>
-      </c>
-      <c r="N101">
-        <v>-147.6629851687203</v>
-      </c>
-      <c r="O101">
-        <v>-29.53259703374406</v>
-      </c>
-      <c r="P101">
-        <v>-118.1303881349762</v>
-      </c>
-      <c r="Q101">
-        <v>-112.3903881349762</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.949483109672124</v>
-      </c>
-      <c r="T101">
-        <v>100.8248859507579</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03098538612721581</v>
-      </c>
-      <c r="W101">
-        <v>0.2284936459512025</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1549269306360791</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
